--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/Github Page/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="272" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8DC8638-F73C-41F6-9882-6031DF8E1118}"/>
+  <xr:revisionPtr revIDLastSave="273" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56E56946-D4C4-40CC-98E6-66DD3CFD70AD}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -260,10 +260,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -356,6 +356,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -570,15 +574,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1146,15 +1150,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1187,7 +1191,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" s="10">
         <v>5</v>
@@ -1669,7 +1673,7 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>2818</v>
+        <v>2819</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/Github Page/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="273" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56E56946-D4C4-40CC-98E6-66DD3CFD70AD}"/>
+  <xr:revisionPtr revIDLastSave="274" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F109AD5-1109-474A-8F4F-E0AAFC63DC4C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -260,10 +260,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -574,15 +574,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1150,15 +1150,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1191,7 +1191,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="10">
         <v>5</v>
@@ -1673,7 +1673,7 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>2819</v>
+        <v>2820</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/Github Page/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="274" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F109AD5-1109-474A-8F4F-E0AAFC63DC4C}"/>
+  <xr:revisionPtr revIDLastSave="276" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A90F6805-B2B0-4D31-ADDD-F8DC49F74440}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="4800" yWindow="2810" windowWidth="14400" windowHeight="7270" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -1191,7 +1191,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="10">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D3" s="10">
         <v>5</v>
@@ -1237,7 +1237,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" s="10">
         <v>5</v>
@@ -1673,7 +1673,7 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>2820</v>
+        <v>2826</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/Github Page/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="276" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A90F6805-B2B0-4D31-ADDD-F8DC49F74440}"/>
+  <xr:revisionPtr revIDLastSave="272" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8DC8638-F73C-41F6-9882-6031DF8E1118}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4800" yWindow="2810" windowWidth="14400" windowHeight="7270" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -358,10 +358,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1191,7 +1187,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="10">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D3" s="10">
         <v>5</v>
@@ -1237,7 +1233,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="10">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" s="10">
         <v>5</v>
@@ -1673,7 +1669,7 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>2826</v>
+        <v>2818</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/Github Page/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="272" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8DC8638-F73C-41F6-9882-6031DF8E1118}"/>
+  <xr:revisionPtr revIDLastSave="278" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54894668-A194-4E43-866D-EDCBC2E34C8F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -260,10 +260,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -356,6 +356,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -570,15 +574,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1146,15 +1150,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1187,7 +1191,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="10">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D3" s="10">
         <v>5</v>
@@ -1669,7 +1673,7 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>2818</v>
+        <v>2824</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/Github Page/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="278" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54894668-A194-4E43-866D-EDCBC2E34C8F}"/>
+  <xr:revisionPtr revIDLastSave="272" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8DC8638-F73C-41F6-9882-6031DF8E1118}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -260,10 +260,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -356,10 +356,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -574,15 +570,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1150,15 +1146,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1191,7 +1187,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="10">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D3" s="10">
         <v>5</v>
@@ -1673,7 +1669,7 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>2824</v>
+        <v>2818</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/Github Page/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="272" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8DC8638-F73C-41F6-9882-6031DF8E1118}"/>
+  <xr:revisionPtr revIDLastSave="280" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27A94A3F-B659-4563-A33F-7A362F5E0903}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -260,10 +260,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -356,6 +356,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -570,15 +574,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1146,15 +1150,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1187,7 +1191,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="10">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D3" s="10">
         <v>5</v>
@@ -1669,7 +1673,7 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>2818</v>
+        <v>2824</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/Github Page/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="280" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27A94A3F-B659-4563-A33F-7A362F5E0903}"/>
+  <xr:revisionPtr revIDLastSave="284" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAC32908-1CD8-42E2-AE35-267B9A4FC435}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -136,13 +136,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -234,42 +241,44 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{2A7B4C8D-CF62-45FF-9CCC-85DEC562C81B}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{E9B108D6-091D-421B-A008-306D5267DFAA}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -614,20 +623,20 @@
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="10">
-        <v>0</v>
-      </c>
-      <c r="D3" s="10">
-        <v>5</v>
-      </c>
-      <c r="E3" s="10">
-        <v>1</v>
-      </c>
-      <c r="F3" s="10">
-        <v>6</v>
-      </c>
-      <c r="G3" s="10">
-        <v>65647</v>
+      <c r="C3" s="12">
+        <v>0</v>
+      </c>
+      <c r="D3" s="12">
+        <v>7</v>
+      </c>
+      <c r="E3" s="12">
+        <v>1</v>
+      </c>
+      <c r="F3" s="12">
+        <v>8</v>
+      </c>
+      <c r="G3" s="12">
+        <v>68212</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -637,19 +646,19 @@
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="12">
         <v>6</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="12">
         <v>3</v>
       </c>
-      <c r="E4" s="10">
-        <v>1</v>
-      </c>
-      <c r="F4" s="10">
-        <v>10</v>
-      </c>
-      <c r="G4" s="10">
+      <c r="E4" s="12">
+        <v>1</v>
+      </c>
+      <c r="F4" s="12">
+        <v>10</v>
+      </c>
+      <c r="G4" s="12">
         <v>96409</v>
       </c>
     </row>
@@ -660,19 +669,19 @@
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="10">
-        <v>0</v>
-      </c>
-      <c r="D5" s="10">
+      <c r="C5" s="12">
+        <v>0</v>
+      </c>
+      <c r="D5" s="12">
         <v>2</v>
       </c>
-      <c r="E5" s="10">
-        <v>1</v>
-      </c>
-      <c r="F5" s="10">
+      <c r="E5" s="12">
+        <v>1</v>
+      </c>
+      <c r="F5" s="12">
         <v>3</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="12">
         <v>10510</v>
       </c>
     </row>
@@ -683,20 +692,20 @@
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="10">
-        <v>3</v>
-      </c>
-      <c r="D6" s="10">
-        <v>1</v>
-      </c>
-      <c r="E6" s="10">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10">
+      <c r="C6" s="12">
         <v>4</v>
       </c>
-      <c r="G6" s="10">
-        <v>12097</v>
+      <c r="D6" s="12">
+        <v>1</v>
+      </c>
+      <c r="E6" s="12">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12">
+        <v>5</v>
+      </c>
+      <c r="G6" s="12">
+        <v>13059</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -706,19 +715,19 @@
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="10">
-        <v>1</v>
-      </c>
-      <c r="D7" s="10">
+      <c r="C7" s="12">
+        <v>1</v>
+      </c>
+      <c r="D7" s="12">
         <v>4</v>
       </c>
-      <c r="E7" s="10">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10">
+      <c r="E7" s="12">
+        <v>0</v>
+      </c>
+      <c r="F7" s="12">
         <v>5</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="12">
         <v>78701</v>
       </c>
     </row>
@@ -729,20 +738,20 @@
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="10">
-        <v>4</v>
-      </c>
-      <c r="D8" s="10">
-        <v>7</v>
-      </c>
-      <c r="E8" s="10">
-        <v>3</v>
-      </c>
-      <c r="F8" s="10">
-        <v>14</v>
-      </c>
-      <c r="G8" s="10">
-        <v>105083</v>
+      <c r="C8" s="12">
+        <v>5</v>
+      </c>
+      <c r="D8" s="12">
+        <v>8</v>
+      </c>
+      <c r="E8" s="12">
+        <v>2</v>
+      </c>
+      <c r="F8" s="12">
+        <v>15</v>
+      </c>
+      <c r="G8" s="12">
+        <v>145860</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -752,19 +761,19 @@
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="10">
-        <v>0</v>
-      </c>
-      <c r="D9" s="10">
-        <v>1</v>
-      </c>
-      <c r="E9" s="10">
-        <v>0</v>
-      </c>
-      <c r="F9" s="10">
-        <v>1</v>
-      </c>
-      <c r="G9" s="10">
+      <c r="C9" s="12">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12">
+        <v>1</v>
+      </c>
+      <c r="E9" s="12">
+        <v>1</v>
+      </c>
+      <c r="F9" s="12">
+        <v>2</v>
+      </c>
+      <c r="G9" s="12">
         <v>26096</v>
       </c>
     </row>
@@ -775,20 +784,20 @@
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="10">
-        <v>0</v>
-      </c>
-      <c r="D10" s="10">
+      <c r="C10" s="12">
+        <v>1</v>
+      </c>
+      <c r="D10" s="12">
         <v>6</v>
       </c>
-      <c r="E10" s="10">
-        <v>1</v>
-      </c>
-      <c r="F10" s="10">
-        <v>7</v>
-      </c>
-      <c r="G10" s="10">
-        <v>215970</v>
+      <c r="E10" s="12">
+        <v>1</v>
+      </c>
+      <c r="F10" s="12">
+        <v>8</v>
+      </c>
+      <c r="G10" s="12">
+        <v>228192</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -798,20 +807,20 @@
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="10">
-        <v>9</v>
-      </c>
-      <c r="D11" s="10">
-        <v>5</v>
-      </c>
-      <c r="E11" s="10">
-        <v>1</v>
-      </c>
-      <c r="F11" s="10">
-        <v>15</v>
-      </c>
-      <c r="G11" s="10">
-        <v>253754</v>
+      <c r="C11" s="12">
+        <v>10</v>
+      </c>
+      <c r="D11" s="12">
+        <v>7</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12">
+        <v>17</v>
+      </c>
+      <c r="G11" s="12">
+        <v>275347</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -821,20 +830,20 @@
       <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="12">
         <v>2</v>
       </c>
-      <c r="D12" s="10">
-        <v>0</v>
-      </c>
-      <c r="E12" s="10">
-        <v>1</v>
-      </c>
-      <c r="F12" s="10">
+      <c r="D12" s="12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="12">
         <v>3</v>
       </c>
-      <c r="G12" s="10">
-        <v>16671</v>
+      <c r="G12" s="12">
+        <v>18470</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -844,20 +853,20 @@
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="10">
-        <v>1</v>
-      </c>
-      <c r="D13" s="10">
+      <c r="C13" s="12">
+        <v>1</v>
+      </c>
+      <c r="D13" s="12">
         <v>9</v>
       </c>
-      <c r="E13" s="10">
-        <v>1</v>
-      </c>
-      <c r="F13" s="10">
+      <c r="E13" s="12">
+        <v>1</v>
+      </c>
+      <c r="F13" s="12">
         <v>11</v>
       </c>
-      <c r="G13" s="10">
-        <v>89564</v>
+      <c r="G13" s="12">
+        <v>110566</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -867,20 +876,20 @@
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="10">
-        <v>19</v>
-      </c>
-      <c r="D14" s="10">
-        <v>7</v>
-      </c>
-      <c r="E14" s="10">
-        <v>1</v>
-      </c>
-      <c r="F14" s="10">
-        <v>27</v>
-      </c>
-      <c r="G14" s="10">
-        <v>52487</v>
+      <c r="C14" s="12">
+        <v>22</v>
+      </c>
+      <c r="D14" s="12">
+        <v>8</v>
+      </c>
+      <c r="E14" s="12">
+        <v>1</v>
+      </c>
+      <c r="F14" s="12">
+        <v>31</v>
+      </c>
+      <c r="G14" s="12">
+        <v>54388</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -890,19 +899,19 @@
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="12">
         <v>7</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="12">
         <v>2</v>
       </c>
-      <c r="E15" s="10">
-        <v>0</v>
-      </c>
-      <c r="F15" s="10">
+      <c r="E15" s="12">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12">
         <v>9</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="12">
         <v>50917</v>
       </c>
     </row>
@@ -913,19 +922,19 @@
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="12">
         <v>3</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="12">
         <v>3</v>
       </c>
-      <c r="E16" s="10">
-        <v>1</v>
-      </c>
-      <c r="F16" s="10">
+      <c r="E16" s="12">
+        <v>1</v>
+      </c>
+      <c r="F16" s="12">
         <v>7</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="12">
         <v>48111</v>
       </c>
     </row>
@@ -936,19 +945,19 @@
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="10">
-        <v>0</v>
-      </c>
-      <c r="D17" s="10">
+      <c r="C17" s="12">
+        <v>0</v>
+      </c>
+      <c r="D17" s="12">
         <v>4</v>
       </c>
-      <c r="E17" s="10">
-        <v>1</v>
-      </c>
-      <c r="F17" s="10">
+      <c r="E17" s="12">
+        <v>1</v>
+      </c>
+      <c r="F17" s="12">
         <v>5</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="12">
         <v>30817</v>
       </c>
     </row>
@@ -959,19 +968,19 @@
       <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="10">
-        <v>0</v>
-      </c>
-      <c r="D18" s="10">
+      <c r="C18" s="12">
+        <v>0</v>
+      </c>
+      <c r="D18" s="12">
         <v>2</v>
       </c>
-      <c r="E18" s="10">
-        <v>1</v>
-      </c>
-      <c r="F18" s="10">
+      <c r="E18" s="12">
+        <v>1</v>
+      </c>
+      <c r="F18" s="12">
         <v>3</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="12">
         <v>32406</v>
       </c>
     </row>
@@ -982,19 +991,19 @@
       <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="10">
-        <v>10</v>
-      </c>
-      <c r="D19" s="10">
-        <v>0</v>
-      </c>
-      <c r="E19" s="10">
-        <v>1</v>
-      </c>
-      <c r="F19" s="10">
+      <c r="C19" s="12">
+        <v>10</v>
+      </c>
+      <c r="D19" s="12">
+        <v>0</v>
+      </c>
+      <c r="E19" s="12">
+        <v>1</v>
+      </c>
+      <c r="F19" s="12">
         <v>11</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="12">
         <v>48424</v>
       </c>
     </row>
@@ -1005,20 +1014,20 @@
       <c r="B20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="10">
-        <v>2</v>
-      </c>
-      <c r="D20" s="10">
-        <v>0</v>
-      </c>
-      <c r="E20" s="10">
-        <v>1</v>
-      </c>
-      <c r="F20" s="10">
+      <c r="C20" s="12">
         <v>3</v>
       </c>
-      <c r="G20" s="10">
-        <v>7264</v>
+      <c r="D20" s="12">
+        <v>0</v>
+      </c>
+      <c r="E20" s="12">
+        <v>1</v>
+      </c>
+      <c r="F20" s="12">
+        <v>4</v>
+      </c>
+      <c r="G20" s="12">
+        <v>11467</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1028,20 +1037,20 @@
       <c r="B21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="10">
-        <v>12</v>
-      </c>
-      <c r="D21" s="10">
+      <c r="C21" s="12">
+        <v>15</v>
+      </c>
+      <c r="D21" s="12">
         <v>6</v>
       </c>
-      <c r="E21" s="10">
-        <v>0</v>
-      </c>
-      <c r="F21" s="10">
-        <v>18</v>
-      </c>
-      <c r="G21" s="10">
-        <v>237002</v>
+      <c r="E21" s="12">
+        <v>0</v>
+      </c>
+      <c r="F21" s="12">
+        <v>21</v>
+      </c>
+      <c r="G21" s="12">
+        <v>242668</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1051,19 +1060,19 @@
       <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="12">
         <v>7</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="12">
         <v>3</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="12">
         <v>3</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="12">
         <v>13</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="12">
         <v>123625</v>
       </c>
     </row>
@@ -1074,20 +1083,20 @@
       <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="12">
         <v>3</v>
       </c>
-      <c r="D23" s="10">
-        <v>5</v>
-      </c>
-      <c r="E23" s="10">
-        <v>1</v>
-      </c>
-      <c r="F23" s="10">
-        <v>9</v>
-      </c>
-      <c r="G23" s="10">
-        <v>54910</v>
+      <c r="D23" s="12">
+        <v>6</v>
+      </c>
+      <c r="E23" s="12">
+        <v>1</v>
+      </c>
+      <c r="F23" s="12">
+        <v>10</v>
+      </c>
+      <c r="G23" s="12">
+        <v>54979</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1097,23 +1106,23 @@
       <c r="B24" s="5"/>
       <c r="C24" s="6">
         <f>SUM(C3:C23)</f>
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D24" s="6">
         <f>SUM(D3:D23)</f>
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E24" s="6">
         <f>SUM(E3:E23)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F24" s="6">
         <f>SUM(F3:F23)</f>
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="G24" s="6">
         <f>SUM(G3:G23)</f>
-        <v>1656465</v>
+        <v>1769224</v>
       </c>
     </row>
   </sheetData>
@@ -1150,15 +1159,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1190,20 +1199,20 @@
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="10">
-        <v>35</v>
-      </c>
-      <c r="D3" s="10">
-        <v>5</v>
-      </c>
-      <c r="E3" s="10">
+      <c r="C3" s="12">
+        <v>36</v>
+      </c>
+      <c r="D3" s="12">
+        <v>7</v>
+      </c>
+      <c r="E3" s="12">
         <v>20</v>
       </c>
-      <c r="F3" s="10">
-        <v>54</v>
-      </c>
-      <c r="G3" s="10">
-        <v>133411</v>
+      <c r="F3" s="12">
+        <v>63</v>
+      </c>
+      <c r="G3" s="12">
+        <v>155299</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1213,20 +1222,20 @@
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="10">
-        <v>156</v>
-      </c>
-      <c r="D4" s="10">
-        <v>15</v>
-      </c>
-      <c r="E4" s="10">
-        <v>27</v>
-      </c>
-      <c r="F4" s="10">
-        <v>198</v>
-      </c>
-      <c r="G4" s="10">
-        <v>272809</v>
+      <c r="C4" s="12">
+        <v>180</v>
+      </c>
+      <c r="D4" s="12">
+        <v>14</v>
+      </c>
+      <c r="E4" s="12">
+        <v>25</v>
+      </c>
+      <c r="F4" s="12">
+        <v>219</v>
+      </c>
+      <c r="G4" s="12">
+        <v>308774</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1236,20 +1245,20 @@
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="10">
-        <v>28</v>
-      </c>
-      <c r="D5" s="10">
-        <v>5</v>
-      </c>
-      <c r="E5" s="10">
-        <v>15</v>
-      </c>
-      <c r="F5" s="10">
-        <v>48</v>
-      </c>
-      <c r="G5" s="10">
-        <v>191453</v>
+      <c r="C5" s="12">
+        <v>34</v>
+      </c>
+      <c r="D5" s="12">
+        <v>6</v>
+      </c>
+      <c r="E5" s="12">
+        <v>16</v>
+      </c>
+      <c r="F5" s="12">
+        <v>56</v>
+      </c>
+      <c r="G5" s="12">
+        <v>264634</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1259,20 +1268,20 @@
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="10">
-        <v>260</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0</v>
-      </c>
-      <c r="E6" s="10">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10">
-        <v>260</v>
-      </c>
-      <c r="G6" s="10">
-        <v>65311</v>
+      <c r="C6" s="12">
+        <v>281</v>
+      </c>
+      <c r="D6" s="12">
+        <v>0</v>
+      </c>
+      <c r="E6" s="12">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12">
+        <v>281</v>
+      </c>
+      <c r="G6" s="12">
+        <v>65416</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1282,20 +1291,20 @@
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="10">
-        <v>170</v>
-      </c>
-      <c r="D7" s="10">
+      <c r="C7" s="12">
+        <v>196</v>
+      </c>
+      <c r="D7" s="12">
         <v>40</v>
       </c>
-      <c r="E7" s="10">
-        <v>27</v>
-      </c>
-      <c r="F7" s="10">
-        <v>237</v>
-      </c>
-      <c r="G7" s="10">
-        <v>2034615</v>
+      <c r="E7" s="12">
+        <v>25</v>
+      </c>
+      <c r="F7" s="12">
+        <v>261</v>
+      </c>
+      <c r="G7" s="12">
+        <v>2299052</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1305,20 +1314,20 @@
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="10">
-        <v>111</v>
-      </c>
-      <c r="D8" s="10">
-        <v>19</v>
-      </c>
-      <c r="E8" s="10">
-        <v>32</v>
-      </c>
-      <c r="F8" s="10">
-        <v>162</v>
-      </c>
-      <c r="G8" s="10">
-        <v>529727</v>
+      <c r="C8" s="12">
+        <v>133</v>
+      </c>
+      <c r="D8" s="12">
+        <v>23</v>
+      </c>
+      <c r="E8" s="12">
+        <v>31</v>
+      </c>
+      <c r="F8" s="12">
+        <v>187</v>
+      </c>
+      <c r="G8" s="12">
+        <v>606047</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1328,19 +1337,19 @@
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="10">
-        <v>0</v>
-      </c>
-      <c r="D9" s="10">
+      <c r="C9" s="12">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12">
         <v>3</v>
       </c>
-      <c r="E9" s="10">
-        <v>0</v>
-      </c>
-      <c r="F9" s="10">
+      <c r="E9" s="12">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12">
         <v>3</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="12">
         <v>17056</v>
       </c>
     </row>
@@ -1351,20 +1360,20 @@
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="10">
-        <v>41</v>
-      </c>
-      <c r="D10" s="10">
+      <c r="C10" s="12">
+        <v>48</v>
+      </c>
+      <c r="D10" s="12">
         <v>12</v>
       </c>
-      <c r="E10" s="10">
-        <v>22</v>
-      </c>
-      <c r="F10" s="10">
-        <v>75</v>
-      </c>
-      <c r="G10" s="10">
-        <v>305460</v>
+      <c r="E10" s="12">
+        <v>21</v>
+      </c>
+      <c r="F10" s="12">
+        <v>81</v>
+      </c>
+      <c r="G10" s="12">
+        <v>358182</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1374,20 +1383,20 @@
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="10">
-        <v>223</v>
-      </c>
-      <c r="D11" s="10">
-        <v>56</v>
-      </c>
-      <c r="E11" s="10">
-        <v>27</v>
-      </c>
-      <c r="F11" s="10">
-        <v>306</v>
-      </c>
-      <c r="G11" s="10">
-        <v>3752452</v>
+      <c r="C11" s="12">
+        <v>249</v>
+      </c>
+      <c r="D11" s="12">
+        <v>51</v>
+      </c>
+      <c r="E11" s="12">
+        <v>26</v>
+      </c>
+      <c r="F11" s="12">
+        <v>326</v>
+      </c>
+      <c r="G11" s="12">
+        <v>4127340</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1397,20 +1406,20 @@
       <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="10">
-        <v>171</v>
-      </c>
-      <c r="D12" s="10">
-        <v>36</v>
-      </c>
-      <c r="E12" s="10">
+      <c r="C12" s="12">
+        <v>195</v>
+      </c>
+      <c r="D12" s="12">
         <v>34</v>
       </c>
-      <c r="F12" s="10">
-        <v>241</v>
-      </c>
-      <c r="G12" s="10">
-        <v>1243164</v>
+      <c r="E12" s="12">
+        <v>35</v>
+      </c>
+      <c r="F12" s="12">
+        <v>264</v>
+      </c>
+      <c r="G12" s="12">
+        <v>1408019</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1420,20 +1429,20 @@
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="10">
-        <v>47</v>
-      </c>
-      <c r="D13" s="10">
-        <v>25</v>
-      </c>
-      <c r="E13" s="10">
+      <c r="C13" s="12">
+        <v>53</v>
+      </c>
+      <c r="D13" s="12">
+        <v>28</v>
+      </c>
+      <c r="E13" s="12">
         <v>20</v>
       </c>
-      <c r="F13" s="10">
-        <v>92</v>
-      </c>
-      <c r="G13" s="10">
-        <v>580644</v>
+      <c r="F13" s="12">
+        <v>101</v>
+      </c>
+      <c r="G13" s="12">
+        <v>638346</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1443,20 +1452,20 @@
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="10">
-        <v>351</v>
-      </c>
-      <c r="D14" s="10">
-        <v>29</v>
-      </c>
-      <c r="E14" s="10">
-        <v>15</v>
-      </c>
-      <c r="F14" s="10">
-        <v>395</v>
-      </c>
-      <c r="G14" s="10">
-        <v>475899</v>
+      <c r="C14" s="12">
+        <v>372</v>
+      </c>
+      <c r="D14" s="12">
+        <v>27</v>
+      </c>
+      <c r="E14" s="12">
+        <v>13</v>
+      </c>
+      <c r="F14" s="12">
+        <v>412</v>
+      </c>
+      <c r="G14" s="12">
+        <v>517975</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1466,20 +1475,20 @@
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="10">
-        <v>241</v>
-      </c>
-      <c r="D15" s="10">
-        <v>24</v>
-      </c>
-      <c r="E15" s="10">
-        <v>19</v>
-      </c>
-      <c r="F15" s="10">
-        <v>284</v>
-      </c>
-      <c r="G15" s="10">
-        <v>806908</v>
+      <c r="C15" s="12">
+        <v>266</v>
+      </c>
+      <c r="D15" s="12">
+        <v>23</v>
+      </c>
+      <c r="E15" s="12">
+        <v>18</v>
+      </c>
+      <c r="F15" s="12">
+        <v>307</v>
+      </c>
+      <c r="G15" s="12">
+        <v>866041</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1489,20 +1498,20 @@
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="10">
-        <v>127</v>
-      </c>
-      <c r="D16" s="10">
+      <c r="C16" s="12">
+        <v>149</v>
+      </c>
+      <c r="D16" s="12">
         <v>19</v>
       </c>
-      <c r="E16" s="10">
-        <v>26</v>
-      </c>
-      <c r="F16" s="10">
-        <v>172</v>
-      </c>
-      <c r="G16" s="10">
-        <v>690707</v>
+      <c r="E16" s="12">
+        <v>27</v>
+      </c>
+      <c r="F16" s="12">
+        <v>195</v>
+      </c>
+      <c r="G16" s="12">
+        <v>786575</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1512,20 +1521,20 @@
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="10">
-        <v>90</v>
-      </c>
-      <c r="D17" s="10">
-        <v>37</v>
-      </c>
-      <c r="E17" s="10">
+      <c r="C17" s="12">
+        <v>108</v>
+      </c>
+      <c r="D17" s="12">
+        <v>44</v>
+      </c>
+      <c r="E17" s="12">
         <v>26</v>
       </c>
-      <c r="F17" s="10">
-        <v>153</v>
-      </c>
-      <c r="G17" s="10">
-        <v>1815101</v>
+      <c r="F17" s="12">
+        <v>178</v>
+      </c>
+      <c r="G17" s="12">
+        <v>2222126</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1535,20 +1544,20 @@
       <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="10">
-        <v>28</v>
-      </c>
-      <c r="D18" s="10">
-        <v>3</v>
-      </c>
-      <c r="E18" s="10">
+      <c r="C18" s="12">
+        <v>34</v>
+      </c>
+      <c r="D18" s="12">
+        <v>5</v>
+      </c>
+      <c r="E18" s="12">
         <v>15</v>
       </c>
-      <c r="F18" s="10">
-        <v>46</v>
-      </c>
-      <c r="G18" s="10">
-        <v>88591</v>
+      <c r="F18" s="12">
+        <v>54</v>
+      </c>
+      <c r="G18" s="12">
+        <v>148478</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1558,20 +1567,20 @@
       <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="10">
-        <v>165</v>
-      </c>
-      <c r="D19" s="10">
-        <v>11</v>
-      </c>
-      <c r="E19" s="10">
-        <v>20</v>
-      </c>
-      <c r="F19" s="10">
-        <v>196</v>
-      </c>
-      <c r="G19" s="10">
-        <v>370958</v>
+      <c r="C19" s="12">
+        <v>189</v>
+      </c>
+      <c r="D19" s="12">
+        <v>9</v>
+      </c>
+      <c r="E19" s="12">
+        <v>19</v>
+      </c>
+      <c r="F19" s="12">
+        <v>217</v>
+      </c>
+      <c r="G19" s="12">
+        <v>394461</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1581,20 +1590,20 @@
       <c r="B20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="10">
-        <v>35</v>
-      </c>
-      <c r="D20" s="10">
-        <v>1</v>
-      </c>
-      <c r="E20" s="10">
+      <c r="C20" s="12">
+        <v>43</v>
+      </c>
+      <c r="D20" s="12">
+        <v>1</v>
+      </c>
+      <c r="E20" s="12">
         <v>21</v>
       </c>
-      <c r="F20" s="10">
-        <v>57</v>
-      </c>
-      <c r="G20" s="10">
-        <v>64637</v>
+      <c r="F20" s="12">
+        <v>65</v>
+      </c>
+      <c r="G20" s="12">
+        <v>83952</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1604,20 +1613,20 @@
       <c r="B21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="10">
-        <v>315</v>
-      </c>
-      <c r="D21" s="10">
+      <c r="C21" s="12">
+        <v>335</v>
+      </c>
+      <c r="D21" s="12">
         <v>25</v>
       </c>
-      <c r="E21" s="10">
-        <v>15</v>
-      </c>
-      <c r="F21" s="10">
-        <v>355</v>
-      </c>
-      <c r="G21" s="10">
-        <v>907579</v>
+      <c r="E21" s="12">
+        <v>14</v>
+      </c>
+      <c r="F21" s="12">
+        <v>374</v>
+      </c>
+      <c r="G21" s="12">
+        <v>949325</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1627,20 +1636,20 @@
       <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="10">
-        <v>172</v>
-      </c>
-      <c r="D22" s="10">
-        <v>28</v>
-      </c>
-      <c r="E22" s="10">
+      <c r="C22" s="12">
+        <v>196</v>
+      </c>
+      <c r="D22" s="12">
+        <v>30</v>
+      </c>
+      <c r="E22" s="12">
         <v>25</v>
       </c>
-      <c r="F22" s="10">
-        <v>225</v>
-      </c>
-      <c r="G22" s="10">
-        <v>690784</v>
+      <c r="F22" s="12">
+        <v>251</v>
+      </c>
+      <c r="G22" s="12">
+        <v>830918</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1650,20 +1659,20 @@
       <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="10">
-        <v>58</v>
-      </c>
-      <c r="D23" s="10">
+      <c r="C23" s="12">
+        <v>66</v>
+      </c>
+      <c r="D23" s="12">
         <v>6</v>
       </c>
-      <c r="E23" s="10">
-        <v>14</v>
-      </c>
-      <c r="F23" s="10">
-        <v>78</v>
-      </c>
-      <c r="G23" s="10">
-        <v>114884</v>
+      <c r="E23" s="12">
+        <v>15</v>
+      </c>
+      <c r="F23" s="12">
+        <v>87</v>
+      </c>
+      <c r="G23" s="12">
+        <v>125243</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1673,23 +1682,23 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>2824</v>
+        <v>3163</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>3637</v>
+        <v>3982</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>15152150</v>
+        <v>17173259</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/Github Page/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="284" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAC32908-1CD8-42E2-AE35-267B9A4FC435}"/>
+  <xr:revisionPtr revIDLastSave="287" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3498258E-74E0-49C6-A010-135395FC1D90}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -136,13 +136,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -241,44 +248,47 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{2A7B4C8D-CF62-45FF-9CCC-85DEC562C81B}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{E9B108D6-091D-421B-A008-306D5267DFAA}"/>
+    <cellStyle name="Normal 4" xfId="3" xr:uid="{FF3209FF-43E1-4592-89B8-4DD7F27D0E55}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -583,15 +593,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -623,20 +633,20 @@
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="12">
-        <v>0</v>
-      </c>
-      <c r="D3" s="12">
-        <v>7</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12">
+      <c r="C3" s="11">
+        <v>1</v>
+      </c>
+      <c r="D3" s="11">
+        <v>6</v>
+      </c>
+      <c r="E3" s="11">
+        <v>1</v>
+      </c>
+      <c r="F3" s="11">
         <v>8</v>
       </c>
-      <c r="G3" s="12">
-        <v>68212</v>
+      <c r="G3" s="11">
+        <v>75414</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -646,20 +656,20 @@
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <v>6</v>
       </c>
-      <c r="D4" s="12">
-        <v>3</v>
-      </c>
-      <c r="E4" s="12">
-        <v>1</v>
-      </c>
-      <c r="F4" s="12">
-        <v>10</v>
-      </c>
-      <c r="G4" s="12">
-        <v>96409</v>
+      <c r="D4" s="11">
+        <v>4</v>
+      </c>
+      <c r="E4" s="11">
+        <v>1</v>
+      </c>
+      <c r="F4" s="11">
+        <v>11</v>
+      </c>
+      <c r="G4" s="11">
+        <v>97148</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -669,20 +679,20 @@
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <v>0</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <v>2</v>
       </c>
-      <c r="E5" s="12">
-        <v>1</v>
-      </c>
-      <c r="F5" s="12">
+      <c r="E5" s="11">
+        <v>1</v>
+      </c>
+      <c r="F5" s="11">
         <v>3</v>
       </c>
-      <c r="G5" s="12">
-        <v>10510</v>
+      <c r="G5" s="11">
+        <v>10617</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -692,19 +702,19 @@
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <v>4</v>
       </c>
-      <c r="D6" s="12">
-        <v>1</v>
-      </c>
-      <c r="E6" s="12">
+      <c r="D6" s="11">
+        <v>1</v>
+      </c>
+      <c r="E6" s="11">
         <v>0</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <v>5</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="11">
         <v>13059</v>
       </c>
     </row>
@@ -715,19 +725,19 @@
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="12">
-        <v>1</v>
-      </c>
-      <c r="D7" s="12">
+      <c r="C7" s="11">
+        <v>1</v>
+      </c>
+      <c r="D7" s="11">
         <v>4</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <v>0</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="11">
         <v>5</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="11">
         <v>78701</v>
       </c>
     </row>
@@ -738,20 +748,20 @@
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <v>5</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>8</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <v>2</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="11">
         <v>15</v>
       </c>
-      <c r="G8" s="12">
-        <v>145860</v>
+      <c r="G8" s="11">
+        <v>150963</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -761,19 +771,19 @@
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <v>0</v>
       </c>
-      <c r="D9" s="12">
-        <v>1</v>
-      </c>
-      <c r="E9" s="12">
-        <v>1</v>
-      </c>
-      <c r="F9" s="12">
+      <c r="D9" s="11">
+        <v>1</v>
+      </c>
+      <c r="E9" s="11">
+        <v>1</v>
+      </c>
+      <c r="F9" s="11">
         <v>2</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="11">
         <v>26096</v>
       </c>
     </row>
@@ -784,19 +794,19 @@
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="12">
-        <v>1</v>
-      </c>
-      <c r="D10" s="12">
+      <c r="C10" s="11">
+        <v>1</v>
+      </c>
+      <c r="D10" s="11">
         <v>6</v>
       </c>
-      <c r="E10" s="12">
-        <v>1</v>
-      </c>
-      <c r="F10" s="12">
+      <c r="E10" s="11">
+        <v>1</v>
+      </c>
+      <c r="F10" s="11">
         <v>8</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="11">
         <v>228192</v>
       </c>
     </row>
@@ -807,19 +817,19 @@
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="12">
-        <v>10</v>
-      </c>
-      <c r="D11" s="12">
+      <c r="C11" s="11">
+        <v>10</v>
+      </c>
+      <c r="D11" s="11">
         <v>7</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="11">
         <v>0</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="11">
         <v>17</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="11">
         <v>275347</v>
       </c>
     </row>
@@ -830,19 +840,19 @@
       <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <v>2</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <v>0</v>
       </c>
-      <c r="E12" s="12">
-        <v>1</v>
-      </c>
-      <c r="F12" s="12">
+      <c r="E12" s="11">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11">
         <v>3</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="11">
         <v>18470</v>
       </c>
     </row>
@@ -853,19 +863,19 @@
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="12">
-        <v>1</v>
-      </c>
-      <c r="D13" s="12">
+      <c r="C13" s="11">
+        <v>1</v>
+      </c>
+      <c r="D13" s="11">
         <v>9</v>
       </c>
-      <c r="E13" s="12">
-        <v>1</v>
-      </c>
-      <c r="F13" s="12">
+      <c r="E13" s="11">
+        <v>1</v>
+      </c>
+      <c r="F13" s="11">
         <v>11</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="11">
         <v>110566</v>
       </c>
     </row>
@@ -876,20 +886,20 @@
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="12">
-        <v>22</v>
-      </c>
-      <c r="D14" s="12">
+      <c r="C14" s="11">
+        <v>23</v>
+      </c>
+      <c r="D14" s="11">
         <v>8</v>
       </c>
-      <c r="E14" s="12">
-        <v>1</v>
-      </c>
-      <c r="F14" s="12">
-        <v>31</v>
-      </c>
-      <c r="G14" s="12">
-        <v>54388</v>
+      <c r="E14" s="11">
+        <v>1</v>
+      </c>
+      <c r="F14" s="11">
+        <v>32</v>
+      </c>
+      <c r="G14" s="11">
+        <v>54796</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -899,19 +909,19 @@
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <v>7</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <v>2</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="11">
         <v>0</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="11">
         <v>9</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="11">
         <v>50917</v>
       </c>
     </row>
@@ -922,19 +932,19 @@
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <v>3</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <v>3</v>
       </c>
-      <c r="E16" s="12">
-        <v>1</v>
-      </c>
-      <c r="F16" s="12">
+      <c r="E16" s="11">
+        <v>1</v>
+      </c>
+      <c r="F16" s="11">
         <v>7</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="11">
         <v>48111</v>
       </c>
     </row>
@@ -945,19 +955,19 @@
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <v>0</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="11">
         <v>4</v>
       </c>
-      <c r="E17" s="12">
-        <v>1</v>
-      </c>
-      <c r="F17" s="12">
+      <c r="E17" s="11">
+        <v>1</v>
+      </c>
+      <c r="F17" s="11">
         <v>5</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="11">
         <v>30817</v>
       </c>
     </row>
@@ -968,20 +978,20 @@
       <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <v>0</v>
       </c>
-      <c r="D18" s="12">
-        <v>2</v>
-      </c>
-      <c r="E18" s="12">
-        <v>1</v>
-      </c>
-      <c r="F18" s="12">
+      <c r="D18" s="11">
         <v>3</v>
       </c>
-      <c r="G18" s="12">
-        <v>32406</v>
+      <c r="E18" s="11">
+        <v>1</v>
+      </c>
+      <c r="F18" s="11">
+        <v>4</v>
+      </c>
+      <c r="G18" s="11">
+        <v>40970</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -991,19 +1001,19 @@
       <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="12">
-        <v>10</v>
-      </c>
-      <c r="D19" s="12">
+      <c r="C19" s="11">
+        <v>10</v>
+      </c>
+      <c r="D19" s="11">
         <v>0</v>
       </c>
-      <c r="E19" s="12">
-        <v>1</v>
-      </c>
-      <c r="F19" s="12">
+      <c r="E19" s="11">
+        <v>1</v>
+      </c>
+      <c r="F19" s="11">
         <v>11</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="11">
         <v>48424</v>
       </c>
     </row>
@@ -1014,19 +1024,19 @@
       <c r="B20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <v>3</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="11">
         <v>0</v>
       </c>
-      <c r="E20" s="12">
-        <v>1</v>
-      </c>
-      <c r="F20" s="12">
+      <c r="E20" s="11">
+        <v>1</v>
+      </c>
+      <c r="F20" s="11">
         <v>4</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="11">
         <v>11467</v>
       </c>
     </row>
@@ -1037,19 +1047,19 @@
       <c r="B21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <v>15</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="11">
         <v>6</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="11">
         <v>0</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="11">
         <v>21</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="11">
         <v>242668</v>
       </c>
     </row>
@@ -1060,19 +1070,19 @@
       <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="11">
         <v>7</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="11">
         <v>3</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="11">
         <v>3</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="11">
         <v>13</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="11">
         <v>123625</v>
       </c>
     </row>
@@ -1083,19 +1093,19 @@
       <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="11">
         <v>3</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="11">
         <v>6</v>
       </c>
-      <c r="E23" s="12">
-        <v>1</v>
-      </c>
-      <c r="F23" s="12">
-        <v>10</v>
-      </c>
-      <c r="G23" s="12">
+      <c r="E23" s="11">
+        <v>1</v>
+      </c>
+      <c r="F23" s="11">
+        <v>10</v>
+      </c>
+      <c r="G23" s="11">
         <v>54979</v>
       </c>
     </row>
@@ -1106,11 +1116,11 @@
       <c r="B24" s="5"/>
       <c r="C24" s="6">
         <f>SUM(C3:C23)</f>
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D24" s="6">
         <f>SUM(D3:D23)</f>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E24" s="6">
         <f>SUM(E3:E23)</f>
@@ -1118,11 +1128,11 @@
       </c>
       <c r="F24" s="6">
         <f>SUM(F3:F23)</f>
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G24" s="6">
         <f>SUM(G3:G23)</f>
-        <v>1769224</v>
+        <v>1791347</v>
       </c>
     </row>
   </sheetData>
@@ -1159,15 +1169,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1199,19 +1209,19 @@
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="10">
         <v>36</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="10">
         <v>7</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="10">
         <v>20</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="10">
         <v>63</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="10">
         <v>155299</v>
       </c>
     </row>
@@ -1222,20 +1232,20 @@
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="12">
-        <v>180</v>
-      </c>
-      <c r="D4" s="12">
-        <v>14</v>
-      </c>
-      <c r="E4" s="12">
-        <v>25</v>
-      </c>
-      <c r="F4" s="12">
-        <v>219</v>
-      </c>
-      <c r="G4" s="12">
-        <v>308774</v>
+      <c r="C4" s="10">
+        <v>184</v>
+      </c>
+      <c r="D4" s="10">
+        <v>16</v>
+      </c>
+      <c r="E4" s="10">
+        <v>24</v>
+      </c>
+      <c r="F4" s="10">
+        <v>224</v>
+      </c>
+      <c r="G4" s="10">
+        <v>322444</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1245,19 +1255,19 @@
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="10">
         <v>34</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="10">
         <v>6</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="10">
         <v>16</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="10">
         <v>56</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="10">
         <v>264634</v>
       </c>
     </row>
@@ -1268,19 +1278,19 @@
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="12">
-        <v>281</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="C6" s="10">
+        <v>287</v>
+      </c>
+      <c r="D6" s="10">
         <v>0</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>0</v>
       </c>
-      <c r="F6" s="12">
-        <v>281</v>
-      </c>
-      <c r="G6" s="12">
+      <c r="F6" s="10">
+        <v>287</v>
+      </c>
+      <c r="G6" s="10">
         <v>65416</v>
       </c>
     </row>
@@ -1291,20 +1301,20 @@
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="12">
-        <v>196</v>
-      </c>
-      <c r="D7" s="12">
-        <v>40</v>
-      </c>
-      <c r="E7" s="12">
-        <v>25</v>
-      </c>
-      <c r="F7" s="12">
-        <v>261</v>
-      </c>
-      <c r="G7" s="12">
-        <v>2299052</v>
+      <c r="C7" s="10">
+        <v>207</v>
+      </c>
+      <c r="D7" s="10">
+        <v>37</v>
+      </c>
+      <c r="E7" s="10">
+        <v>22</v>
+      </c>
+      <c r="F7" s="10">
+        <v>266</v>
+      </c>
+      <c r="G7" s="10">
+        <v>2392030</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1314,20 +1324,20 @@
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="12">
-        <v>133</v>
-      </c>
-      <c r="D8" s="12">
+      <c r="C8" s="10">
+        <v>137</v>
+      </c>
+      <c r="D8" s="10">
         <v>23</v>
       </c>
-      <c r="E8" s="12">
-        <v>31</v>
-      </c>
-      <c r="F8" s="12">
-        <v>187</v>
-      </c>
-      <c r="G8" s="12">
-        <v>606047</v>
+      <c r="E8" s="10">
+        <v>30</v>
+      </c>
+      <c r="F8" s="10">
+        <v>190</v>
+      </c>
+      <c r="G8" s="10">
+        <v>623081</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1337,19 +1347,19 @@
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="10">
         <v>0</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="10">
         <v>3</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="10">
         <v>0</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="10">
         <v>3</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="10">
         <v>17056</v>
       </c>
     </row>
@@ -1360,20 +1370,20 @@
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="10">
         <v>48</v>
       </c>
-      <c r="D10" s="12">
-        <v>12</v>
-      </c>
-      <c r="E10" s="12">
+      <c r="D10" s="10">
+        <v>13</v>
+      </c>
+      <c r="E10" s="10">
         <v>21</v>
       </c>
-      <c r="F10" s="12">
-        <v>81</v>
-      </c>
-      <c r="G10" s="12">
-        <v>358182</v>
+      <c r="F10" s="10">
+        <v>82</v>
+      </c>
+      <c r="G10" s="10">
+        <v>377259</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1383,20 +1393,20 @@
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="12">
-        <v>249</v>
-      </c>
-      <c r="D11" s="12">
-        <v>51</v>
-      </c>
-      <c r="E11" s="12">
+      <c r="C11" s="10">
+        <v>258</v>
+      </c>
+      <c r="D11" s="10">
+        <v>47</v>
+      </c>
+      <c r="E11" s="10">
         <v>26</v>
       </c>
-      <c r="F11" s="12">
-        <v>326</v>
-      </c>
-      <c r="G11" s="12">
-        <v>4127340</v>
+      <c r="F11" s="10">
+        <v>331</v>
+      </c>
+      <c r="G11" s="10">
+        <v>4246989</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1406,20 +1416,20 @@
       <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="12">
-        <v>195</v>
-      </c>
-      <c r="D12" s="12">
+      <c r="C12" s="10">
+        <v>209</v>
+      </c>
+      <c r="D12" s="10">
         <v>34</v>
       </c>
-      <c r="E12" s="12">
-        <v>35</v>
-      </c>
-      <c r="F12" s="12">
-        <v>264</v>
-      </c>
-      <c r="G12" s="12">
-        <v>1408019</v>
+      <c r="E12" s="10">
+        <v>29</v>
+      </c>
+      <c r="F12" s="10">
+        <v>272</v>
+      </c>
+      <c r="G12" s="10">
+        <v>1514686</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1429,20 +1439,20 @@
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="12">
-        <v>53</v>
-      </c>
-      <c r="D13" s="12">
-        <v>28</v>
-      </c>
-      <c r="E13" s="12">
+      <c r="C13" s="10">
+        <v>55</v>
+      </c>
+      <c r="D13" s="10">
+        <v>27</v>
+      </c>
+      <c r="E13" s="10">
         <v>20</v>
       </c>
-      <c r="F13" s="12">
-        <v>101</v>
-      </c>
-      <c r="G13" s="12">
-        <v>638346</v>
+      <c r="F13" s="10">
+        <v>102</v>
+      </c>
+      <c r="G13" s="10">
+        <v>648138</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1452,20 +1462,20 @@
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="12">
-        <v>372</v>
-      </c>
-      <c r="D14" s="12">
+      <c r="C14" s="10">
+        <v>377</v>
+      </c>
+      <c r="D14" s="10">
         <v>27</v>
       </c>
-      <c r="E14" s="12">
-        <v>13</v>
-      </c>
-      <c r="F14" s="12">
-        <v>412</v>
-      </c>
-      <c r="G14" s="12">
-        <v>517975</v>
+      <c r="E14" s="10">
+        <v>12</v>
+      </c>
+      <c r="F14" s="10">
+        <v>416</v>
+      </c>
+      <c r="G14" s="10">
+        <v>522251</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1475,20 +1485,20 @@
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="12">
-        <v>266</v>
-      </c>
-      <c r="D15" s="12">
-        <v>23</v>
-      </c>
-      <c r="E15" s="12">
-        <v>18</v>
-      </c>
-      <c r="F15" s="12">
-        <v>307</v>
-      </c>
-      <c r="G15" s="12">
-        <v>866041</v>
+      <c r="C15" s="10">
+        <v>273</v>
+      </c>
+      <c r="D15" s="10">
+        <v>25</v>
+      </c>
+      <c r="E15" s="10">
+        <v>16</v>
+      </c>
+      <c r="F15" s="10">
+        <v>314</v>
+      </c>
+      <c r="G15" s="10">
+        <v>886034</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1498,20 +1508,20 @@
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="12">
-        <v>149</v>
-      </c>
-      <c r="D16" s="12">
-        <v>19</v>
-      </c>
-      <c r="E16" s="12">
-        <v>27</v>
-      </c>
-      <c r="F16" s="12">
-        <v>195</v>
-      </c>
-      <c r="G16" s="12">
-        <v>786575</v>
+      <c r="C16" s="10">
+        <v>154</v>
+      </c>
+      <c r="D16" s="10">
+        <v>20</v>
+      </c>
+      <c r="E16" s="10">
+        <v>24</v>
+      </c>
+      <c r="F16" s="10">
+        <v>198</v>
+      </c>
+      <c r="G16" s="10">
+        <v>819044</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1521,20 +1531,20 @@
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="12">
-        <v>108</v>
-      </c>
-      <c r="D17" s="12">
-        <v>44</v>
-      </c>
-      <c r="E17" s="12">
-        <v>26</v>
-      </c>
-      <c r="F17" s="12">
-        <v>178</v>
-      </c>
-      <c r="G17" s="12">
-        <v>2222126</v>
+      <c r="C17" s="10">
+        <v>110</v>
+      </c>
+      <c r="D17" s="10">
+        <v>46</v>
+      </c>
+      <c r="E17" s="10">
+        <v>25</v>
+      </c>
+      <c r="F17" s="10">
+        <v>181</v>
+      </c>
+      <c r="G17" s="10">
+        <v>2362832</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1544,20 +1554,20 @@
       <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="12">
-        <v>34</v>
-      </c>
-      <c r="D18" s="12">
-        <v>5</v>
-      </c>
-      <c r="E18" s="12">
+      <c r="C18" s="10">
+        <v>35</v>
+      </c>
+      <c r="D18" s="10">
+        <v>4</v>
+      </c>
+      <c r="E18" s="10">
         <v>15</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="10">
         <v>54</v>
       </c>
-      <c r="G18" s="12">
-        <v>148478</v>
+      <c r="G18" s="10">
+        <v>164537</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1567,20 +1577,20 @@
       <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="12">
-        <v>189</v>
-      </c>
-      <c r="D19" s="12">
-        <v>9</v>
-      </c>
-      <c r="E19" s="12">
-        <v>19</v>
-      </c>
-      <c r="F19" s="12">
-        <v>217</v>
-      </c>
-      <c r="G19" s="12">
-        <v>394461</v>
+      <c r="C19" s="10">
+        <v>193</v>
+      </c>
+      <c r="D19" s="10">
+        <v>12</v>
+      </c>
+      <c r="E19" s="10">
+        <v>18</v>
+      </c>
+      <c r="F19" s="10">
+        <v>223</v>
+      </c>
+      <c r="G19" s="10">
+        <v>408719</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1590,20 +1600,20 @@
       <c r="B20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="10">
         <v>43</v>
       </c>
-      <c r="D20" s="12">
-        <v>1</v>
-      </c>
-      <c r="E20" s="12">
+      <c r="D20" s="10">
+        <v>1</v>
+      </c>
+      <c r="E20" s="10">
         <v>21</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="10">
         <v>65</v>
       </c>
-      <c r="G20" s="12">
-        <v>83952</v>
+      <c r="G20" s="10">
+        <v>84859</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1613,20 +1623,20 @@
       <c r="B21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="12">
-        <v>335</v>
-      </c>
-      <c r="D21" s="12">
-        <v>25</v>
-      </c>
-      <c r="E21" s="12">
-        <v>14</v>
-      </c>
-      <c r="F21" s="12">
-        <v>374</v>
-      </c>
-      <c r="G21" s="12">
-        <v>949325</v>
+      <c r="C21" s="10">
+        <v>342</v>
+      </c>
+      <c r="D21" s="10">
+        <v>24</v>
+      </c>
+      <c r="E21" s="10">
+        <v>13</v>
+      </c>
+      <c r="F21" s="10">
+        <v>379</v>
+      </c>
+      <c r="G21" s="10">
+        <v>962110</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1636,20 +1646,20 @@
       <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="12">
-        <v>196</v>
-      </c>
-      <c r="D22" s="12">
-        <v>30</v>
-      </c>
-      <c r="E22" s="12">
-        <v>25</v>
-      </c>
-      <c r="F22" s="12">
-        <v>251</v>
-      </c>
-      <c r="G22" s="12">
-        <v>830918</v>
+      <c r="C22" s="10">
+        <v>207</v>
+      </c>
+      <c r="D22" s="10">
+        <v>28</v>
+      </c>
+      <c r="E22" s="10">
+        <v>24</v>
+      </c>
+      <c r="F22" s="10">
+        <v>259</v>
+      </c>
+      <c r="G22" s="10">
+        <v>871616</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1659,20 +1669,20 @@
       <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="12">
-        <v>66</v>
-      </c>
-      <c r="D23" s="12">
-        <v>6</v>
-      </c>
-      <c r="E23" s="12">
+      <c r="C23" s="10">
+        <v>67</v>
+      </c>
+      <c r="D23" s="10">
+        <v>7</v>
+      </c>
+      <c r="E23" s="10">
         <v>15</v>
       </c>
-      <c r="F23" s="12">
-        <v>87</v>
-      </c>
-      <c r="G23" s="12">
-        <v>125243</v>
+      <c r="F23" s="10">
+        <v>89</v>
+      </c>
+      <c r="G23" s="10">
+        <v>129677</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1682,7 +1692,7 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>3163</v>
+        <v>3256</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
@@ -1690,15 +1700,15 @@
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>3982</v>
+        <v>4054</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>17173259</v>
+        <v>17838711</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/Github Page/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="287" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3498258E-74E0-49C6-A010-135395FC1D90}"/>
+  <xr:revisionPtr revIDLastSave="293" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE3C7BBC-A361-4189-AACF-77BEA2FCAECE}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -136,13 +136,27 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -248,47 +262,50 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{2A7B4C8D-CF62-45FF-9CCC-85DEC562C81B}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{E9B108D6-091D-421B-A008-306D5267DFAA}"/>
     <cellStyle name="Normal 4" xfId="3" xr:uid="{FF3209FF-43E1-4592-89B8-4DD7F27D0E55}"/>
+    <cellStyle name="Normal 5" xfId="4" xr:uid="{F92F8613-E883-4456-B695-57F219B68B51}"/>
+    <cellStyle name="Normal 6" xfId="5" xr:uid="{69E69302-DAF2-4240-AB0E-8FB6A14C8934}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -593,15 +610,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -633,19 +650,19 @@
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="11">
-        <v>1</v>
-      </c>
-      <c r="D3" s="11">
+      <c r="C3" s="12">
+        <v>1</v>
+      </c>
+      <c r="D3" s="12">
         <v>6</v>
       </c>
-      <c r="E3" s="11">
-        <v>1</v>
-      </c>
-      <c r="F3" s="11">
+      <c r="E3" s="12">
+        <v>1</v>
+      </c>
+      <c r="F3" s="12">
         <v>8</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="12">
         <v>75414</v>
       </c>
     </row>
@@ -656,19 +673,19 @@
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="12">
         <v>6</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="12">
         <v>4</v>
       </c>
-      <c r="E4" s="11">
-        <v>1</v>
-      </c>
-      <c r="F4" s="11">
+      <c r="E4" s="12">
+        <v>1</v>
+      </c>
+      <c r="F4" s="12">
         <v>11</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="12">
         <v>97148</v>
       </c>
     </row>
@@ -679,19 +696,19 @@
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="12">
         <v>0</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="12">
         <v>2</v>
       </c>
-      <c r="E5" s="11">
-        <v>1</v>
-      </c>
-      <c r="F5" s="11">
+      <c r="E5" s="12">
+        <v>1</v>
+      </c>
+      <c r="F5" s="12">
         <v>3</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="12">
         <v>10617</v>
       </c>
     </row>
@@ -702,19 +719,19 @@
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="12">
         <v>4</v>
       </c>
-      <c r="D6" s="11">
-        <v>1</v>
-      </c>
-      <c r="E6" s="11">
+      <c r="D6" s="12">
+        <v>1</v>
+      </c>
+      <c r="E6" s="12">
         <v>0</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="12">
         <v>5</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="12">
         <v>13059</v>
       </c>
     </row>
@@ -725,20 +742,20 @@
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="11">
-        <v>1</v>
-      </c>
-      <c r="D7" s="11">
+      <c r="C7" s="12">
+        <v>1</v>
+      </c>
+      <c r="D7" s="12">
         <v>4</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="12">
         <v>0</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="12">
         <v>5</v>
       </c>
-      <c r="G7" s="11">
-        <v>78701</v>
+      <c r="G7" s="12">
+        <v>80741</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -748,20 +765,20 @@
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="11">
-        <v>5</v>
-      </c>
-      <c r="D8" s="11">
-        <v>8</v>
-      </c>
-      <c r="E8" s="11">
+      <c r="C8" s="12">
+        <v>6</v>
+      </c>
+      <c r="D8" s="12">
+        <v>7</v>
+      </c>
+      <c r="E8" s="12">
         <v>2</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="12">
         <v>15</v>
       </c>
-      <c r="G8" s="11">
-        <v>150963</v>
+      <c r="G8" s="12">
+        <v>158415</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -771,19 +788,19 @@
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="12">
         <v>0</v>
       </c>
-      <c r="D9" s="11">
-        <v>1</v>
-      </c>
-      <c r="E9" s="11">
-        <v>1</v>
-      </c>
-      <c r="F9" s="11">
+      <c r="D9" s="12">
+        <v>1</v>
+      </c>
+      <c r="E9" s="12">
+        <v>1</v>
+      </c>
+      <c r="F9" s="12">
         <v>2</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="12">
         <v>26096</v>
       </c>
     </row>
@@ -794,19 +811,19 @@
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="11">
-        <v>1</v>
-      </c>
-      <c r="D10" s="11">
+      <c r="C10" s="12">
+        <v>1</v>
+      </c>
+      <c r="D10" s="12">
         <v>6</v>
       </c>
-      <c r="E10" s="11">
-        <v>1</v>
-      </c>
-      <c r="F10" s="11">
+      <c r="E10" s="12">
+        <v>1</v>
+      </c>
+      <c r="F10" s="12">
         <v>8</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="12">
         <v>228192</v>
       </c>
     </row>
@@ -817,20 +834,20 @@
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="11">
-        <v>10</v>
-      </c>
-      <c r="D11" s="11">
+      <c r="C11" s="12">
+        <v>10</v>
+      </c>
+      <c r="D11" s="12">
         <v>7</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="12">
         <v>0</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="12">
         <v>17</v>
       </c>
-      <c r="G11" s="11">
-        <v>275347</v>
+      <c r="G11" s="12">
+        <v>281648</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -840,19 +857,19 @@
       <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="12">
         <v>2</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="12">
         <v>0</v>
       </c>
-      <c r="E12" s="11">
-        <v>1</v>
-      </c>
-      <c r="F12" s="11">
+      <c r="E12" s="12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="12">
         <v>3</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="12">
         <v>18470</v>
       </c>
     </row>
@@ -863,20 +880,20 @@
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="11">
-        <v>1</v>
-      </c>
-      <c r="D13" s="11">
-        <v>9</v>
-      </c>
-      <c r="E13" s="11">
-        <v>1</v>
-      </c>
-      <c r="F13" s="11">
-        <v>11</v>
-      </c>
-      <c r="G13" s="11">
-        <v>110566</v>
+      <c r="C13" s="12">
+        <v>1</v>
+      </c>
+      <c r="D13" s="12">
+        <v>10</v>
+      </c>
+      <c r="E13" s="12">
+        <v>1</v>
+      </c>
+      <c r="F13" s="12">
+        <v>12</v>
+      </c>
+      <c r="G13" s="12">
+        <v>110632</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -886,19 +903,19 @@
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="12">
         <v>23</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="12">
         <v>8</v>
       </c>
-      <c r="E14" s="11">
-        <v>1</v>
-      </c>
-      <c r="F14" s="11">
+      <c r="E14" s="12">
+        <v>1</v>
+      </c>
+      <c r="F14" s="12">
         <v>32</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="12">
         <v>54796</v>
       </c>
     </row>
@@ -909,19 +926,19 @@
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="12">
         <v>7</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="12">
         <v>2</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="12">
         <v>0</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="12">
         <v>9</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="12">
         <v>50917</v>
       </c>
     </row>
@@ -932,19 +949,19 @@
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="12">
         <v>3</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="12">
         <v>3</v>
       </c>
-      <c r="E16" s="11">
-        <v>1</v>
-      </c>
-      <c r="F16" s="11">
+      <c r="E16" s="12">
+        <v>1</v>
+      </c>
+      <c r="F16" s="12">
         <v>7</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="12">
         <v>48111</v>
       </c>
     </row>
@@ -955,19 +972,19 @@
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="12">
         <v>0</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="12">
         <v>4</v>
       </c>
-      <c r="E17" s="11">
-        <v>1</v>
-      </c>
-      <c r="F17" s="11">
+      <c r="E17" s="12">
+        <v>1</v>
+      </c>
+      <c r="F17" s="12">
         <v>5</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="12">
         <v>30817</v>
       </c>
     </row>
@@ -978,19 +995,19 @@
       <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="12">
         <v>0</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="12">
         <v>3</v>
       </c>
-      <c r="E18" s="11">
-        <v>1</v>
-      </c>
-      <c r="F18" s="11">
+      <c r="E18" s="12">
+        <v>1</v>
+      </c>
+      <c r="F18" s="12">
         <v>4</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="12">
         <v>40970</v>
       </c>
     </row>
@@ -1001,19 +1018,19 @@
       <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="11">
-        <v>10</v>
-      </c>
-      <c r="D19" s="11">
+      <c r="C19" s="12">
+        <v>10</v>
+      </c>
+      <c r="D19" s="12">
         <v>0</v>
       </c>
-      <c r="E19" s="11">
-        <v>1</v>
-      </c>
-      <c r="F19" s="11">
+      <c r="E19" s="12">
+        <v>1</v>
+      </c>
+      <c r="F19" s="12">
         <v>11</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="12">
         <v>48424</v>
       </c>
     </row>
@@ -1024,19 +1041,19 @@
       <c r="B20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="12">
         <v>3</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="12">
         <v>0</v>
       </c>
-      <c r="E20" s="11">
-        <v>1</v>
-      </c>
-      <c r="F20" s="11">
+      <c r="E20" s="12">
+        <v>1</v>
+      </c>
+      <c r="F20" s="12">
         <v>4</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="12">
         <v>11467</v>
       </c>
     </row>
@@ -1047,19 +1064,19 @@
       <c r="B21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="12">
         <v>15</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="12">
         <v>6</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="12">
         <v>0</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="12">
         <v>21</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="12">
         <v>242668</v>
       </c>
     </row>
@@ -1070,20 +1087,20 @@
       <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="11">
-        <v>7</v>
-      </c>
-      <c r="D22" s="11">
+      <c r="C22" s="12">
+        <v>8</v>
+      </c>
+      <c r="D22" s="12">
         <v>3</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="12">
         <v>3</v>
       </c>
-      <c r="F22" s="11">
-        <v>13</v>
-      </c>
-      <c r="G22" s="11">
-        <v>123625</v>
+      <c r="F22" s="12">
+        <v>14</v>
+      </c>
+      <c r="G22" s="12">
+        <v>128306</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1093,19 +1110,19 @@
       <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="12">
         <v>3</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="12">
         <v>6</v>
       </c>
-      <c r="E23" s="11">
-        <v>1</v>
-      </c>
-      <c r="F23" s="11">
-        <v>10</v>
-      </c>
-      <c r="G23" s="11">
+      <c r="E23" s="12">
+        <v>1</v>
+      </c>
+      <c r="F23" s="12">
+        <v>10</v>
+      </c>
+      <c r="G23" s="12">
         <v>54979</v>
       </c>
     </row>
@@ -1116,7 +1133,7 @@
       <c r="B24" s="5"/>
       <c r="C24" s="6">
         <f>SUM(C3:C23)</f>
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D24" s="6">
         <f>SUM(D3:D23)</f>
@@ -1128,11 +1145,11 @@
       </c>
       <c r="F24" s="6">
         <f>SUM(F3:F23)</f>
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G24" s="6">
         <f>SUM(G3:G23)</f>
-        <v>1791347</v>
+        <v>1811887</v>
       </c>
     </row>
   </sheetData>
@@ -1169,15 +1186,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1209,20 +1226,20 @@
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="10">
-        <v>36</v>
-      </c>
-      <c r="D3" s="10">
+      <c r="C3" s="12">
+        <v>40</v>
+      </c>
+      <c r="D3" s="12">
         <v>7</v>
       </c>
-      <c r="E3" s="10">
-        <v>20</v>
-      </c>
-      <c r="F3" s="10">
-        <v>63</v>
-      </c>
-      <c r="G3" s="10">
-        <v>155299</v>
+      <c r="E3" s="12">
+        <v>19</v>
+      </c>
+      <c r="F3" s="12">
+        <v>66</v>
+      </c>
+      <c r="G3" s="12">
+        <v>198526</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1232,20 +1249,20 @@
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="10">
-        <v>184</v>
-      </c>
-      <c r="D4" s="10">
+      <c r="C4" s="12">
+        <v>207</v>
+      </c>
+      <c r="D4" s="12">
         <v>16</v>
       </c>
-      <c r="E4" s="10">
-        <v>24</v>
-      </c>
-      <c r="F4" s="10">
-        <v>224</v>
-      </c>
-      <c r="G4" s="10">
-        <v>322444</v>
+      <c r="E4" s="12">
+        <v>22</v>
+      </c>
+      <c r="F4" s="12">
+        <v>245</v>
+      </c>
+      <c r="G4" s="12">
+        <v>353263</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1255,20 +1272,20 @@
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="10">
-        <v>34</v>
-      </c>
-      <c r="D5" s="10">
+      <c r="C5" s="12">
+        <v>37</v>
+      </c>
+      <c r="D5" s="12">
         <v>6</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="12">
         <v>16</v>
       </c>
-      <c r="F5" s="10">
-        <v>56</v>
-      </c>
-      <c r="G5" s="10">
-        <v>264634</v>
+      <c r="F5" s="12">
+        <v>59</v>
+      </c>
+      <c r="G5" s="12">
+        <v>276796</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1278,19 +1295,19 @@
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="10">
-        <v>287</v>
-      </c>
-      <c r="D6" s="10">
+      <c r="C6" s="12">
+        <v>302</v>
+      </c>
+      <c r="D6" s="12">
         <v>0</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="12">
         <v>0</v>
       </c>
-      <c r="F6" s="10">
-        <v>287</v>
-      </c>
-      <c r="G6" s="10">
+      <c r="F6" s="12">
+        <v>302</v>
+      </c>
+      <c r="G6" s="12">
         <v>65416</v>
       </c>
     </row>
@@ -1301,20 +1318,20 @@
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="10">
-        <v>207</v>
-      </c>
-      <c r="D7" s="10">
-        <v>37</v>
-      </c>
-      <c r="E7" s="10">
-        <v>22</v>
-      </c>
-      <c r="F7" s="10">
-        <v>266</v>
-      </c>
-      <c r="G7" s="10">
-        <v>2392030</v>
+      <c r="C7" s="12">
+        <v>221</v>
+      </c>
+      <c r="D7" s="12">
+        <v>40</v>
+      </c>
+      <c r="E7" s="12">
+        <v>21</v>
+      </c>
+      <c r="F7" s="12">
+        <v>282</v>
+      </c>
+      <c r="G7" s="12">
+        <v>2581183</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1324,20 +1341,20 @@
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="10">
-        <v>137</v>
-      </c>
-      <c r="D8" s="10">
-        <v>23</v>
-      </c>
-      <c r="E8" s="10">
-        <v>30</v>
-      </c>
-      <c r="F8" s="10">
-        <v>190</v>
-      </c>
-      <c r="G8" s="10">
-        <v>623081</v>
+      <c r="C8" s="12">
+        <v>154</v>
+      </c>
+      <c r="D8" s="12">
+        <v>22</v>
+      </c>
+      <c r="E8" s="12">
+        <v>34</v>
+      </c>
+      <c r="F8" s="12">
+        <v>210</v>
+      </c>
+      <c r="G8" s="12">
+        <v>683226</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1347,19 +1364,19 @@
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="12">
         <v>0</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="12">
         <v>3</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="12">
         <v>0</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="12">
         <v>3</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="12">
         <v>17056</v>
       </c>
     </row>
@@ -1370,20 +1387,20 @@
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="10">
-        <v>48</v>
-      </c>
-      <c r="D10" s="10">
+      <c r="C10" s="12">
+        <v>51</v>
+      </c>
+      <c r="D10" s="12">
         <v>13</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="12">
         <v>21</v>
       </c>
-      <c r="F10" s="10">
-        <v>82</v>
-      </c>
-      <c r="G10" s="10">
-        <v>377259</v>
+      <c r="F10" s="12">
+        <v>85</v>
+      </c>
+      <c r="G10" s="12">
+        <v>382181</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1393,20 +1410,20 @@
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="10">
-        <v>258</v>
-      </c>
-      <c r="D11" s="10">
-        <v>47</v>
-      </c>
-      <c r="E11" s="10">
-        <v>26</v>
-      </c>
-      <c r="F11" s="10">
-        <v>331</v>
-      </c>
-      <c r="G11" s="10">
-        <v>4246989</v>
+      <c r="C11" s="12">
+        <v>276</v>
+      </c>
+      <c r="D11" s="12">
+        <v>44</v>
+      </c>
+      <c r="E11" s="12">
+        <v>25</v>
+      </c>
+      <c r="F11" s="12">
+        <v>345</v>
+      </c>
+      <c r="G11" s="12">
+        <v>4437174</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1416,20 +1433,20 @@
       <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="10">
-        <v>209</v>
-      </c>
-      <c r="D12" s="10">
-        <v>34</v>
-      </c>
-      <c r="E12" s="10">
-        <v>29</v>
-      </c>
-      <c r="F12" s="10">
-        <v>272</v>
-      </c>
-      <c r="G12" s="10">
-        <v>1514686</v>
+      <c r="C12" s="12">
+        <v>226</v>
+      </c>
+      <c r="D12" s="12">
+        <v>33</v>
+      </c>
+      <c r="E12" s="12">
+        <v>27</v>
+      </c>
+      <c r="F12" s="12">
+        <v>286</v>
+      </c>
+      <c r="G12" s="12">
+        <v>1582514</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1439,20 +1456,20 @@
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="10">
-        <v>55</v>
-      </c>
-      <c r="D13" s="10">
-        <v>27</v>
-      </c>
-      <c r="E13" s="10">
-        <v>20</v>
-      </c>
-      <c r="F13" s="10">
-        <v>102</v>
-      </c>
-      <c r="G13" s="10">
-        <v>648138</v>
+      <c r="C13" s="12">
+        <v>58</v>
+      </c>
+      <c r="D13" s="12">
+        <v>31</v>
+      </c>
+      <c r="E13" s="12">
+        <v>19</v>
+      </c>
+      <c r="F13" s="12">
+        <v>108</v>
+      </c>
+      <c r="G13" s="12">
+        <v>684766</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1462,20 +1479,20 @@
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="10">
-        <v>377</v>
-      </c>
-      <c r="D14" s="10">
-        <v>27</v>
-      </c>
-      <c r="E14" s="10">
-        <v>12</v>
-      </c>
-      <c r="F14" s="10">
-        <v>416</v>
-      </c>
-      <c r="G14" s="10">
-        <v>522251</v>
+      <c r="C14" s="12">
+        <v>391</v>
+      </c>
+      <c r="D14" s="12">
+        <v>29</v>
+      </c>
+      <c r="E14" s="12">
+        <v>11</v>
+      </c>
+      <c r="F14" s="12">
+        <v>431</v>
+      </c>
+      <c r="G14" s="12">
+        <v>550547</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1485,20 +1502,20 @@
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="10">
-        <v>273</v>
-      </c>
-      <c r="D15" s="10">
-        <v>25</v>
-      </c>
-      <c r="E15" s="10">
-        <v>16</v>
-      </c>
-      <c r="F15" s="10">
-        <v>314</v>
-      </c>
-      <c r="G15" s="10">
-        <v>886034</v>
+      <c r="C15" s="12">
+        <v>290</v>
+      </c>
+      <c r="D15" s="12">
+        <v>26</v>
+      </c>
+      <c r="E15" s="12">
+        <v>15</v>
+      </c>
+      <c r="F15" s="12">
+        <v>331</v>
+      </c>
+      <c r="G15" s="12">
+        <v>933529</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1508,20 +1525,20 @@
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="10">
-        <v>154</v>
-      </c>
-      <c r="D16" s="10">
-        <v>20</v>
-      </c>
-      <c r="E16" s="10">
-        <v>24</v>
-      </c>
-      <c r="F16" s="10">
-        <v>198</v>
-      </c>
-      <c r="G16" s="10">
-        <v>819044</v>
+      <c r="C16" s="12">
+        <v>174</v>
+      </c>
+      <c r="D16" s="12">
+        <v>21</v>
+      </c>
+      <c r="E16" s="12">
+        <v>26</v>
+      </c>
+      <c r="F16" s="12">
+        <v>221</v>
+      </c>
+      <c r="G16" s="12">
+        <v>955339</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1531,20 +1548,20 @@
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="10">
-        <v>110</v>
-      </c>
-      <c r="D17" s="10">
-        <v>46</v>
-      </c>
-      <c r="E17" s="10">
-        <v>25</v>
-      </c>
-      <c r="F17" s="10">
-        <v>181</v>
-      </c>
-      <c r="G17" s="10">
-        <v>2362832</v>
+      <c r="C17" s="12">
+        <v>130</v>
+      </c>
+      <c r="D17" s="12">
+        <v>47</v>
+      </c>
+      <c r="E17" s="12">
+        <v>27</v>
+      </c>
+      <c r="F17" s="12">
+        <v>204</v>
+      </c>
+      <c r="G17" s="12">
+        <v>2729984</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1554,20 +1571,20 @@
       <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="10">
-        <v>35</v>
-      </c>
-      <c r="D18" s="10">
+      <c r="C18" s="12">
+        <v>38</v>
+      </c>
+      <c r="D18" s="12">
         <v>4</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="12">
         <v>15</v>
       </c>
-      <c r="F18" s="10">
-        <v>54</v>
-      </c>
-      <c r="G18" s="10">
-        <v>164537</v>
+      <c r="F18" s="12">
+        <v>57</v>
+      </c>
+      <c r="G18" s="12">
+        <v>181668</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1577,20 +1594,20 @@
       <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="10">
-        <v>193</v>
-      </c>
-      <c r="D19" s="10">
-        <v>12</v>
-      </c>
-      <c r="E19" s="10">
-        <v>18</v>
-      </c>
-      <c r="F19" s="10">
-        <v>223</v>
-      </c>
-      <c r="G19" s="10">
-        <v>408719</v>
+      <c r="C19" s="12">
+        <v>219</v>
+      </c>
+      <c r="D19" s="12">
+        <v>11</v>
+      </c>
+      <c r="E19" s="12">
+        <v>19</v>
+      </c>
+      <c r="F19" s="12">
+        <v>249</v>
+      </c>
+      <c r="G19" s="12">
+        <v>457337</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1600,20 +1617,20 @@
       <c r="B20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="10">
-        <v>43</v>
-      </c>
-      <c r="D20" s="10">
-        <v>1</v>
-      </c>
-      <c r="E20" s="10">
-        <v>21</v>
-      </c>
-      <c r="F20" s="10">
-        <v>65</v>
-      </c>
-      <c r="G20" s="10">
-        <v>84859</v>
+      <c r="C20" s="12">
+        <v>46</v>
+      </c>
+      <c r="D20" s="12">
+        <v>1</v>
+      </c>
+      <c r="E20" s="12">
+        <v>20</v>
+      </c>
+      <c r="F20" s="12">
+        <v>67</v>
+      </c>
+      <c r="G20" s="12">
+        <v>86478</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1623,20 +1640,20 @@
       <c r="B21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="10">
-        <v>342</v>
-      </c>
-      <c r="D21" s="10">
+      <c r="C21" s="12">
+        <v>358</v>
+      </c>
+      <c r="D21" s="12">
         <v>24</v>
       </c>
-      <c r="E21" s="10">
-        <v>13</v>
-      </c>
-      <c r="F21" s="10">
-        <v>379</v>
-      </c>
-      <c r="G21" s="10">
-        <v>962110</v>
+      <c r="E21" s="12">
+        <v>12</v>
+      </c>
+      <c r="F21" s="12">
+        <v>394</v>
+      </c>
+      <c r="G21" s="12">
+        <v>993757</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1646,20 +1663,20 @@
       <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="10">
-        <v>207</v>
-      </c>
-      <c r="D22" s="10">
+      <c r="C22" s="12">
+        <v>230</v>
+      </c>
+      <c r="D22" s="12">
         <v>28</v>
       </c>
-      <c r="E22" s="10">
-        <v>24</v>
-      </c>
-      <c r="F22" s="10">
-        <v>259</v>
-      </c>
-      <c r="G22" s="10">
-        <v>871616</v>
+      <c r="E22" s="12">
+        <v>23</v>
+      </c>
+      <c r="F22" s="12">
+        <v>281</v>
+      </c>
+      <c r="G22" s="12">
+        <v>952954</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1669,20 +1686,20 @@
       <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="10">
-        <v>67</v>
-      </c>
-      <c r="D23" s="10">
-        <v>7</v>
-      </c>
-      <c r="E23" s="10">
-        <v>15</v>
-      </c>
-      <c r="F23" s="10">
-        <v>89</v>
-      </c>
-      <c r="G23" s="10">
-        <v>129677</v>
+      <c r="C23" s="12">
+        <v>68</v>
+      </c>
+      <c r="D23" s="12">
+        <v>11</v>
+      </c>
+      <c r="E23" s="12">
+        <v>14</v>
+      </c>
+      <c r="F23" s="12">
+        <v>93</v>
+      </c>
+      <c r="G23" s="12">
+        <v>147564</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1692,23 +1709,23 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>3256</v>
+        <v>3516</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>4054</v>
+        <v>4319</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>17838711</v>
+        <v>19251258</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/Github Page/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="293" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE3C7BBC-A361-4189-AACF-77BEA2FCAECE}"/>
+  <xr:revisionPtr revIDLastSave="321" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4388213C-980D-43E8-93D9-5B2A64E9732D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -136,13 +136,34 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -262,8 +283,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -272,40 +296,43 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{2A7B4C8D-CF62-45FF-9CCC-85DEC562C81B}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{E9B108D6-091D-421B-A008-306D5267DFAA}"/>
     <cellStyle name="Normal 4" xfId="3" xr:uid="{FF3209FF-43E1-4592-89B8-4DD7F27D0E55}"/>
     <cellStyle name="Normal 5" xfId="4" xr:uid="{F92F8613-E883-4456-B695-57F219B68B51}"/>
     <cellStyle name="Normal 6" xfId="5" xr:uid="{69E69302-DAF2-4240-AB0E-8FB6A14C8934}"/>
+    <cellStyle name="Normal 7" xfId="6" xr:uid="{6147F187-9489-4094-A911-1ADA2C2FBE09}"/>
+    <cellStyle name="Normal 8" xfId="7" xr:uid="{75BADD7B-DDB8-4F17-9D6E-A3016147D7C3}"/>
+    <cellStyle name="Normal 9" xfId="8" xr:uid="{26DDD18A-BF9E-4DD5-9FD2-4FC278C18433}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -610,15 +637,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -657,10 +684,10 @@
         <v>6</v>
       </c>
       <c r="E3" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="12">
         <v>75414</v>
@@ -674,19 +701,19 @@
         <v>10</v>
       </c>
       <c r="C4" s="12">
+        <v>7</v>
+      </c>
+      <c r="D4" s="12">
         <v>6</v>
       </c>
-      <c r="D4" s="12">
-        <v>4</v>
-      </c>
       <c r="E4" s="12">
         <v>1</v>
       </c>
       <c r="F4" s="12">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4" s="12">
-        <v>97148</v>
+        <v>115713</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -700,16 +727,16 @@
         <v>0</v>
       </c>
       <c r="D5" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" s="12">
-        <v>10617</v>
+        <v>10776</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -720,19 +747,19 @@
         <v>10</v>
       </c>
       <c r="C6" s="12">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D6" s="12">
         <v>1</v>
       </c>
       <c r="E6" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="12">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G6" s="12">
-        <v>13059</v>
+        <v>15132</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -743,19 +770,19 @@
         <v>10</v>
       </c>
       <c r="C7" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G7" s="12">
-        <v>80741</v>
+        <v>89757</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -766,10 +793,10 @@
         <v>10</v>
       </c>
       <c r="C8" s="12">
+        <v>7</v>
+      </c>
+      <c r="D8" s="12">
         <v>6</v>
-      </c>
-      <c r="D8" s="12">
-        <v>7</v>
       </c>
       <c r="E8" s="12">
         <v>2</v>
@@ -778,7 +805,7 @@
         <v>15</v>
       </c>
       <c r="G8" s="12">
-        <v>158415</v>
+        <v>165918</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -815,16 +842,16 @@
         <v>1</v>
       </c>
       <c r="D10" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="12">
-        <v>228192</v>
+        <v>228215</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -835,19 +862,19 @@
         <v>10</v>
       </c>
       <c r="C11" s="12">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D11" s="12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" s="12">
         <v>0</v>
       </c>
       <c r="F11" s="12">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G11" s="12">
-        <v>281648</v>
+        <v>297874</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -858,19 +885,19 @@
         <v>10</v>
       </c>
       <c r="C12" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="12">
         <v>0</v>
       </c>
       <c r="E12" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12" s="12">
-        <v>18470</v>
+        <v>19078</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -884,16 +911,16 @@
         <v>1</v>
       </c>
       <c r="D13" s="12">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E13" s="12">
         <v>1</v>
       </c>
       <c r="F13" s="12">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G13" s="12">
-        <v>110632</v>
+        <v>116608</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -904,19 +931,19 @@
         <v>10</v>
       </c>
       <c r="C14" s="12">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D14" s="12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E14" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="12">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G14" s="12">
-        <v>54796</v>
+        <v>89112</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -927,19 +954,19 @@
         <v>10</v>
       </c>
       <c r="C15" s="12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="12">
         <v>2</v>
       </c>
       <c r="E15" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="12">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G15" s="12">
-        <v>50917</v>
+        <v>51133</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1008,7 +1035,7 @@
         <v>4</v>
       </c>
       <c r="G18" s="12">
-        <v>40970</v>
+        <v>62570</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1019,19 +1046,19 @@
         <v>10</v>
       </c>
       <c r="C19" s="12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="12">
         <v>1</v>
       </c>
       <c r="F19" s="12">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G19" s="12">
-        <v>48424</v>
+        <v>49811</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1065,7 +1092,7 @@
         <v>10</v>
       </c>
       <c r="C21" s="12">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D21" s="12">
         <v>6</v>
@@ -1074,10 +1101,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="12">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G21" s="12">
-        <v>242668</v>
+        <v>255268</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1114,16 +1141,16 @@
         <v>3</v>
       </c>
       <c r="D23" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" s="12">
         <v>1</v>
       </c>
       <c r="F23" s="12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23" s="12">
-        <v>54979</v>
+        <v>55060</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1133,23 +1160,23 @@
       <c r="B24" s="5"/>
       <c r="C24" s="6">
         <f>SUM(C3:C23)</f>
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="D24" s="6">
         <f>SUM(D3:D23)</f>
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E24" s="6">
         <f>SUM(E3:E23)</f>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F24" s="6">
         <f>SUM(F3:F23)</f>
-        <v>206</v>
+        <v>244</v>
       </c>
       <c r="G24" s="6">
         <f>SUM(G3:G23)</f>
-        <v>1811887</v>
+        <v>1942236</v>
       </c>
     </row>
   </sheetData>
@@ -1186,15 +1213,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1227,19 +1254,19 @@
         <v>10</v>
       </c>
       <c r="C3" s="12">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D3" s="12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="12">
         <v>19</v>
       </c>
       <c r="F3" s="12">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G3" s="12">
-        <v>198526</v>
+        <v>319501</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1250,19 +1277,19 @@
         <v>10</v>
       </c>
       <c r="C4" s="12">
-        <v>207</v>
+        <v>265</v>
       </c>
       <c r="D4" s="12">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E4" s="12">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F4" s="12">
-        <v>245</v>
+        <v>296</v>
       </c>
       <c r="G4" s="12">
-        <v>353263</v>
+        <v>453457</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1273,19 +1300,19 @@
         <v>10</v>
       </c>
       <c r="C5" s="12">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D5" s="12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" s="12">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" s="12">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G5" s="12">
-        <v>276796</v>
+        <v>487983</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1296,7 +1323,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="12">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="D6" s="12">
         <v>0</v>
@@ -1305,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="12">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="G6" s="12">
-        <v>65416</v>
+        <v>73788</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1319,19 +1346,19 @@
         <v>10</v>
       </c>
       <c r="C7" s="12">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="D7" s="12">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E7" s="12">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F7" s="12">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="G7" s="12">
-        <v>2581183</v>
+        <v>3041799</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1342,19 +1369,19 @@
         <v>10</v>
       </c>
       <c r="C8" s="12">
-        <v>154</v>
+        <v>235</v>
       </c>
       <c r="D8" s="12">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E8" s="12">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F8" s="12">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="G8" s="12">
-        <v>683226</v>
+        <v>1059365</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1368,16 +1395,16 @@
         <v>0</v>
       </c>
       <c r="D9" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E9" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G9" s="12">
-        <v>17056</v>
+        <v>28932</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1388,19 +1415,19 @@
         <v>10</v>
       </c>
       <c r="C10" s="12">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="D10" s="12">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E10" s="12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="12">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="G10" s="12">
-        <v>382181</v>
+        <v>725664</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1411,19 +1438,19 @@
         <v>10</v>
       </c>
       <c r="C11" s="12">
-        <v>276</v>
+        <v>314</v>
       </c>
       <c r="D11" s="12">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" s="12">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F11" s="12">
-        <v>345</v>
+        <v>380</v>
       </c>
       <c r="G11" s="12">
-        <v>4437174</v>
+        <v>4936173</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1434,19 +1461,19 @@
         <v>10</v>
       </c>
       <c r="C12" s="12">
-        <v>226</v>
+        <v>272</v>
       </c>
       <c r="D12" s="12">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E12" s="12">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F12" s="12">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="G12" s="12">
-        <v>1582514</v>
+        <v>1890931</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1457,19 +1484,19 @@
         <v>10</v>
       </c>
       <c r="C13" s="12">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="D13" s="12">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E13" s="12">
         <v>19</v>
       </c>
       <c r="F13" s="12">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="G13" s="12">
-        <v>684766</v>
+        <v>916969</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1480,19 +1507,19 @@
         <v>10</v>
       </c>
       <c r="C14" s="12">
-        <v>391</v>
+        <v>426</v>
       </c>
       <c r="D14" s="12">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E14" s="12">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F14" s="12">
-        <v>431</v>
+        <v>473</v>
       </c>
       <c r="G14" s="12">
-        <v>550547</v>
+        <v>609886</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1503,19 +1530,19 @@
         <v>10</v>
       </c>
       <c r="C15" s="12">
-        <v>290</v>
+        <v>324</v>
       </c>
       <c r="D15" s="12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="12">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F15" s="12">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="G15" s="12">
-        <v>933529</v>
+        <v>1007046</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1526,19 +1553,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="12">
-        <v>174</v>
+        <v>240</v>
       </c>
       <c r="D16" s="12">
+        <v>18</v>
+      </c>
+      <c r="E16" s="12">
         <v>21</v>
       </c>
-      <c r="E16" s="12">
-        <v>26</v>
-      </c>
       <c r="F16" s="12">
-        <v>221</v>
+        <v>279</v>
       </c>
       <c r="G16" s="12">
-        <v>955339</v>
+        <v>1271938</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1549,19 +1576,19 @@
         <v>10</v>
       </c>
       <c r="C17" s="12">
-        <v>130</v>
+        <v>213</v>
       </c>
       <c r="D17" s="12">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E17" s="12">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F17" s="12">
-        <v>204</v>
+        <v>266</v>
       </c>
       <c r="G17" s="12">
-        <v>2729984</v>
+        <v>3892676</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1572,19 +1599,19 @@
         <v>10</v>
       </c>
       <c r="C18" s="12">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D18" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="12">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F18" s="12">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="G18" s="12">
-        <v>181668</v>
+        <v>292931</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1595,19 +1622,19 @@
         <v>10</v>
       </c>
       <c r="C19" s="12">
-        <v>219</v>
+        <v>276</v>
       </c>
       <c r="D19" s="12">
         <v>11</v>
       </c>
       <c r="E19" s="12">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F19" s="12">
-        <v>249</v>
+        <v>302</v>
       </c>
       <c r="G19" s="12">
-        <v>457337</v>
+        <v>739537</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1618,19 +1645,19 @@
         <v>10</v>
       </c>
       <c r="C20" s="12">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D20" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="12">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F20" s="12">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="G20" s="12">
-        <v>86478</v>
+        <v>134284</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1641,19 +1668,19 @@
         <v>10</v>
       </c>
       <c r="C21" s="12">
-        <v>358</v>
+        <v>395</v>
       </c>
       <c r="D21" s="12">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E21" s="12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F21" s="12">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="G21" s="12">
-        <v>993757</v>
+        <v>1060574</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1664,19 +1691,19 @@
         <v>10</v>
       </c>
       <c r="C22" s="12">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="D22" s="12">
         <v>28</v>
       </c>
       <c r="E22" s="12">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F22" s="12">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="G22" s="12">
-        <v>952954</v>
+        <v>1211769</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1687,19 +1714,19 @@
         <v>10</v>
       </c>
       <c r="C23" s="12">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="D23" s="12">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E23" s="12">
         <v>14</v>
       </c>
       <c r="F23" s="12">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="G23" s="12">
-        <v>147564</v>
+        <v>292934</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1709,23 +1736,23 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>3516</v>
+        <v>4310</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>4319</v>
+        <v>5059</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>19251258</v>
+        <v>24448137</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wisetechglobal-my.sharepoint.com/personal/naseem_ahmad_wisetechglobal_com/Documents/Desktop/Github Page/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="321" documentId="11_7E0858C819626DA01459401D9A7FEF7A1AE13B5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4388213C-980D-43E8-93D9-5B2A64E9732D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4992C86F-D41E-41DF-9692-FDE6A1802B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -66,9 +66,6 @@
     <t>Architecting AI Solutions: Scalable GenAI Systems for the Future</t>
   </si>
   <si>
-    <t>AI Courses</t>
-  </si>
-  <si>
     <t>Boost Your Productivity With AI</t>
   </si>
   <si>
@@ -133,13 +130,16 @@
   </si>
   <si>
     <t>AI Course Enrollment Data – e2open  |  Update this sheet to refresh the dashboard</t>
+  </si>
+  <si>
+    <t>Ai Courses</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -631,7 +631,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -640,7 +640,7 @@
     <col min="7" max="7" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.75" customHeight="1">
+    <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -651,7 +651,7 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
     </row>
-    <row r="2" spans="1:7" ht="21.75" customHeight="1">
+    <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -674,12 +674,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18" customHeight="1">
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C3" s="10">
         <v>1</v>
@@ -697,12 +697,12 @@
         <v>75414</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1">
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C4" s="10">
         <v>7</v>
@@ -720,12 +720,12 @@
         <v>115713</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="18" customHeight="1">
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
@@ -743,12 +743,12 @@
         <v>10776</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="18" customHeight="1">
+    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C6" s="10">
         <v>7</v>
@@ -766,35 +766,35 @@
         <v>15132</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="18" customHeight="1">
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C7" s="10">
         <v>3</v>
       </c>
       <c r="D7" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G7" s="10">
-        <v>89757</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1">
+        <v>100132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C8" s="10">
         <v>7</v>
@@ -803,21 +803,21 @@
         <v>6</v>
       </c>
       <c r="E8" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" s="10">
         <v>165918</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="18" customHeight="1">
+    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C9" s="10">
         <v>0</v>
@@ -832,15 +832,15 @@
         <v>2</v>
       </c>
       <c r="G9" s="10">
-        <v>26096</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18" customHeight="1">
+        <v>26136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C10" s="10">
         <v>1</v>
@@ -858,18 +858,18 @@
         <v>228215</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="18" customHeight="1">
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C11" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" s="10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" s="10">
         <v>0</v>
@@ -878,38 +878,38 @@
         <v>23</v>
       </c>
       <c r="G11" s="10">
-        <v>297874</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1">
+        <v>309506</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C12" s="10">
         <v>3</v>
       </c>
       <c r="D12" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G12" s="10">
-        <v>19078</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="18" customHeight="1">
+        <v>30061</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C13" s="10">
         <v>1</v>
@@ -927,38 +927,38 @@
         <v>116608</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="18" customHeight="1">
+    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C14" s="10">
         <v>28</v>
       </c>
       <c r="D14" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E14" s="10">
         <v>0</v>
       </c>
       <c r="F14" s="10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G14" s="10">
-        <v>89112</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="18" customHeight="1">
+        <v>92087</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="10">
         <v>9</v>
-      </c>
-      <c r="C15" s="10">
-        <v>8</v>
       </c>
       <c r="D15" s="10">
         <v>2</v>
@@ -967,41 +967,41 @@
         <v>1</v>
       </c>
       <c r="F15" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15" s="10">
-        <v>51133</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="18" customHeight="1">
+        <v>53131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C16" s="10">
         <v>3</v>
       </c>
       <c r="D16" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="10">
         <v>1</v>
       </c>
       <c r="F16" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G16" s="10">
-        <v>48111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="18" customHeight="1">
+        <v>62127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C17" s="10">
         <v>0</v>
@@ -1019,12 +1019,12 @@
         <v>30817</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="18" customHeight="1">
+    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C18" s="10">
         <v>0</v>
@@ -1042,38 +1042,38 @@
         <v>62570</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="18" customHeight="1">
+    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="10">
+        <v>12</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10">
+        <v>2</v>
+      </c>
+      <c r="F19" s="10">
+        <v>14</v>
+      </c>
+      <c r="G19" s="10">
+        <v>50365</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="10">
-        <v>11</v>
-      </c>
-      <c r="D19" s="10">
-        <v>1</v>
-      </c>
-      <c r="E19" s="10">
-        <v>1</v>
-      </c>
-      <c r="F19" s="10">
-        <v>13</v>
-      </c>
-      <c r="G19" s="10">
-        <v>49811</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="18" customHeight="1">
-      <c r="A20" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="B20" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C20" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="10">
         <v>0</v>
@@ -1082,18 +1082,18 @@
         <v>1</v>
       </c>
       <c r="F20" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="10">
-        <v>11467</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="18" customHeight="1">
+        <v>24070</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C21" s="10">
         <v>20</v>
@@ -1111,12 +1111,12 @@
         <v>255268</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="18" customHeight="1">
+    <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C22" s="10">
         <v>8</v>
@@ -1134,12 +1134,12 @@
         <v>128306</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="18" customHeight="1">
+    <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C23" s="10">
         <v>3</v>
@@ -1157,30 +1157,30 @@
         <v>55060</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="19.5" customHeight="1">
+    <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="6">
         <f>SUM(C3:C23)</f>
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D24" s="6">
         <f>SUM(D3:D23)</f>
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E24" s="6">
         <f>SUM(E3:E23)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F24" s="6">
         <f>SUM(F3:F23)</f>
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="G24" s="6">
         <f>SUM(G3:G23)</f>
-        <v>1942236</v>
+        <v>2007412</v>
       </c>
     </row>
   </sheetData>
@@ -1207,7 +1207,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1216,9 +1216,9 @@
     <col min="7" max="7" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.75" customHeight="1">
+    <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -1227,7 +1227,7 @@
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
     </row>
-    <row r="2" spans="1:7" ht="21.75" customHeight="1">
+    <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1250,12 +1250,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18" customHeight="1">
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C3" s="10">
         <v>54</v>
@@ -1270,18 +1270,18 @@
         <v>81</v>
       </c>
       <c r="G3" s="10">
-        <v>319501</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1">
+        <v>340505</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C4" s="10">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D4" s="10">
         <v>14</v>
@@ -1290,44 +1290,44 @@
         <v>17</v>
       </c>
       <c r="F4" s="10">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G4" s="10">
-        <v>453457</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18" customHeight="1">
+        <v>456535</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C5" s="10">
         <v>49</v>
       </c>
       <c r="D5" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="10">
         <v>18</v>
       </c>
       <c r="F5" s="10">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G5" s="10">
-        <v>487983</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18" customHeight="1">
+        <v>558711</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C6" s="10">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D6" s="10">
         <v>0</v>
@@ -1336,64 +1336,64 @@
         <v>0</v>
       </c>
       <c r="F6" s="10">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G6" s="10">
-        <v>73788</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18" customHeight="1">
+        <v>75358</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C7" s="10">
         <v>274</v>
       </c>
       <c r="D7" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" s="10">
         <v>19</v>
       </c>
       <c r="F7" s="10">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G7" s="10">
-        <v>3041799</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1">
+        <v>3042699</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C8" s="10">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D8" s="10">
         <v>17</v>
       </c>
       <c r="E8" s="10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F8" s="10">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G8" s="10">
-        <v>1059365</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18" customHeight="1">
+        <v>1081355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C9" s="10">
         <v>0</v>
@@ -1411,81 +1411,81 @@
         <v>28932</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="18" customHeight="1">
+    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C10" s="10">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D10" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" s="10">
         <v>22</v>
       </c>
       <c r="F10" s="10">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G10" s="10">
-        <v>725664</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="18" customHeight="1">
+        <v>757310</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C11" s="10">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D11" s="10">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E11" s="10">
         <v>21</v>
       </c>
       <c r="F11" s="10">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G11" s="10">
-        <v>4936173</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1">
+        <v>5000170</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C12" s="10">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D12" s="10">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E12" s="10">
         <v>23</v>
       </c>
       <c r="F12" s="10">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G12" s="10">
-        <v>1890931</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="18" customHeight="1">
+        <v>1910102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C13" s="10">
         <v>78</v>
@@ -1503,38 +1503,38 @@
         <v>916969</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="18" customHeight="1">
+    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C14" s="10">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D14" s="10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" s="10">
         <v>13</v>
       </c>
       <c r="F14" s="10">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="G14" s="10">
-        <v>609886</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="18" customHeight="1">
+        <v>614670</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C15" s="10">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D15" s="10">
         <v>25</v>
@@ -1543,182 +1543,182 @@
         <v>14</v>
       </c>
       <c r="F15" s="10">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G15" s="10">
-        <v>1007046</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="18" customHeight="1">
+        <v>1011351</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C16" s="10">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D16" s="10">
         <v>18</v>
       </c>
       <c r="E16" s="10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F16" s="10">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G16" s="10">
-        <v>1271938</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="18" customHeight="1">
+        <v>1295858</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C17" s="10">
         <v>213</v>
       </c>
       <c r="D17" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17" s="10">
+        <v>24</v>
+      </c>
+      <c r="F17" s="10">
+        <v>268</v>
+      </c>
+      <c r="G17" s="10">
+        <v>3908257</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="10">
-        <v>266</v>
-      </c>
-      <c r="G17" s="10">
-        <v>3892676</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="18" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="B18" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C18" s="10">
         <v>52</v>
       </c>
       <c r="D18" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="10">
         <v>17</v>
       </c>
       <c r="F18" s="10">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G18" s="10">
-        <v>292931</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="18" customHeight="1">
+        <v>294594</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C19" s="10">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D19" s="10">
         <v>11</v>
       </c>
       <c r="E19" s="10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F19" s="10">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G19" s="10">
-        <v>739537</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="18" customHeight="1">
+        <v>745368</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="10">
+        <v>65</v>
+      </c>
+      <c r="D20" s="10">
+        <v>3</v>
+      </c>
+      <c r="E20" s="10">
+        <v>21</v>
+      </c>
+      <c r="F20" s="10">
+        <v>89</v>
+      </c>
+      <c r="G20" s="10">
+        <v>148491</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="10">
-        <v>64</v>
-      </c>
-      <c r="D20" s="10">
-        <v>2</v>
-      </c>
-      <c r="E20" s="10">
-        <v>22</v>
-      </c>
-      <c r="F20" s="10">
-        <v>88</v>
-      </c>
-      <c r="G20" s="10">
-        <v>134284</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="18" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="B21" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C21" s="10">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D21" s="10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E21" s="10">
         <v>11</v>
       </c>
       <c r="F21" s="10">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="G21" s="10">
-        <v>1060574</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="18" customHeight="1">
+        <v>1075558</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C22" s="10">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D22" s="10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E22" s="10">
         <v>21</v>
       </c>
       <c r="F22" s="10">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G22" s="10">
-        <v>1211769</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="18" customHeight="1">
+        <v>1218083</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C23" s="10">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D23" s="10">
         <v>14</v>
@@ -1727,36 +1727,36 @@
         <v>14</v>
       </c>
       <c r="F23" s="10">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G23" s="10">
-        <v>292934</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="19.5" customHeight="1">
+        <v>296588</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4310</v>
+        <v>4337</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5059</v>
+        <v>5093</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>24448137</v>
+        <v>24777464</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4992C86F-D41E-41DF-9692-FDE6A1802B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03592B3-C478-4771-BC7C-20F873DCE442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -708,16 +708,16 @@
         <v>7</v>
       </c>
       <c r="D4" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" s="10">
         <v>1</v>
       </c>
       <c r="F4" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="10">
-        <v>115713</v>
+        <v>115935</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -774,10 +774,10 @@
         <v>31</v>
       </c>
       <c r="C7" s="10">
+        <v>4</v>
+      </c>
+      <c r="D7" s="10">
         <v>3</v>
-      </c>
-      <c r="D7" s="10">
-        <v>4</v>
       </c>
       <c r="E7" s="10">
         <v>2</v>
@@ -786,7 +786,7 @@
         <v>9</v>
       </c>
       <c r="G7" s="10">
-        <v>100132</v>
+        <v>101585</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -892,16 +892,16 @@
         <v>3</v>
       </c>
       <c r="D12" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="10">
         <v>3</v>
       </c>
       <c r="F12" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" s="10">
-        <v>30061</v>
+        <v>34564</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -984,16 +984,16 @@
         <v>3</v>
       </c>
       <c r="D16" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="10">
         <v>1</v>
       </c>
       <c r="F16" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="10">
-        <v>62127</v>
+        <v>62170</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1007,16 +1007,16 @@
         <v>0</v>
       </c>
       <c r="D17" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="10">
         <v>1</v>
       </c>
       <c r="F17" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17" s="10">
-        <v>30817</v>
+        <v>34419</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1053,16 +1053,16 @@
         <v>12</v>
       </c>
       <c r="D19" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="10">
         <v>2</v>
       </c>
       <c r="F19" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G19" s="10">
-        <v>50365</v>
+        <v>51365</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1122,16 +1122,16 @@
         <v>8</v>
       </c>
       <c r="D22" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="10">
         <v>3</v>
       </c>
       <c r="F22" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G22" s="10">
-        <v>128306</v>
+        <v>130471</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1164,11 +1164,11 @@
       <c r="B24" s="5"/>
       <c r="C24" s="6">
         <f>SUM(C3:C23)</f>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D24" s="6">
         <f>SUM(D3:D23)</f>
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E24" s="6">
         <f>SUM(E3:E23)</f>
@@ -1176,11 +1176,11 @@
       </c>
       <c r="F24" s="6">
         <f>SUM(F3:F23)</f>
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G24" s="6">
         <f>SUM(G3:G23)</f>
-        <v>2007412</v>
+        <v>2020400</v>
       </c>
     </row>
   </sheetData>
@@ -1270,7 +1270,7 @@
         <v>81</v>
       </c>
       <c r="G3" s="10">
-        <v>340505</v>
+        <v>349447</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="E4" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" s="10">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G4" s="10">
         <v>456535</v>
@@ -1316,7 +1316,7 @@
         <v>76</v>
       </c>
       <c r="G5" s="10">
-        <v>558711</v>
+        <v>603857</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1327,7 +1327,7 @@
         <v>31</v>
       </c>
       <c r="C6" s="10">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D6" s="10">
         <v>0</v>
@@ -1336,10 +1336,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="10">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G6" s="10">
-        <v>75358</v>
+        <v>75787</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1350,7 +1350,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="10">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D7" s="10">
         <v>24</v>
@@ -1359,10 +1359,10 @@
         <v>19</v>
       </c>
       <c r="F7" s="10">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G7" s="10">
-        <v>3042699</v>
+        <v>3045072</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1379,10 +1379,10 @@
         <v>17</v>
       </c>
       <c r="E8" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="10">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G8" s="10">
         <v>1081355</v>
@@ -1442,19 +1442,19 @@
         <v>31</v>
       </c>
       <c r="C11" s="10">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D11" s="10">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E11" s="10">
         <v>21</v>
       </c>
       <c r="F11" s="10">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G11" s="10">
-        <v>5000170</v>
+        <v>5013879</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1465,7 +1465,7 @@
         <v>31</v>
       </c>
       <c r="C12" s="10">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D12" s="10">
         <v>31</v>
@@ -1474,10 +1474,10 @@
         <v>23</v>
       </c>
       <c r="F12" s="10">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G12" s="10">
-        <v>1910102</v>
+        <v>1943387</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1491,16 +1491,16 @@
         <v>78</v>
       </c>
       <c r="D13" s="10">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E13" s="10">
         <v>19</v>
       </c>
       <c r="F13" s="10">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G13" s="10">
-        <v>916969</v>
+        <v>916984</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1511,19 +1511,19 @@
         <v>31</v>
       </c>
       <c r="C14" s="10">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D14" s="10">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" s="10">
         <v>13</v>
       </c>
       <c r="F14" s="10">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G14" s="10">
-        <v>614670</v>
+        <v>615396</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1534,19 +1534,19 @@
         <v>31</v>
       </c>
       <c r="C15" s="10">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D15" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="10">
         <v>14</v>
       </c>
       <c r="F15" s="10">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="G15" s="10">
-        <v>1011351</v>
+        <v>1023459</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1557,7 +1557,7 @@
         <v>31</v>
       </c>
       <c r="C16" s="10">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D16" s="10">
         <v>18</v>
@@ -1566,10 +1566,10 @@
         <v>19</v>
       </c>
       <c r="F16" s="10">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G16" s="10">
-        <v>1295858</v>
+        <v>1309416</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1586,10 +1586,10 @@
         <v>31</v>
       </c>
       <c r="E17" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F17" s="10">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G17" s="10">
         <v>3908257</v>
@@ -1615,7 +1615,7 @@
         <v>73</v>
       </c>
       <c r="G18" s="10">
-        <v>294594</v>
+        <v>296533</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1632,10 +1632,10 @@
         <v>11</v>
       </c>
       <c r="E19" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F19" s="10">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G19" s="10">
         <v>745368</v>
@@ -1661,7 +1661,7 @@
         <v>89</v>
       </c>
       <c r="G20" s="10">
-        <v>148491</v>
+        <v>149308</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1672,19 +1672,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="10">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D21" s="10">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E21" s="10">
         <v>11</v>
       </c>
       <c r="F21" s="10">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G21" s="10">
-        <v>1075558</v>
+        <v>1077922</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1701,10 +1701,10 @@
         <v>27</v>
       </c>
       <c r="E22" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="10">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G22" s="10">
         <v>1218083</v>
@@ -1740,23 +1740,23 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4337</v>
+        <v>4351</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5093</v>
+        <v>5110</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>24777464</v>
+        <v>24912875</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03592B3-C478-4771-BC7C-20F873DCE442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B514E5B-7199-4E77-9A17-0538452BF155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -1016,7 +1016,7 @@
         <v>6</v>
       </c>
       <c r="G17" s="10">
-        <v>34419</v>
+        <v>39210</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1050,7 +1050,7 @@
         <v>31</v>
       </c>
       <c r="C19" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" s="10">
         <v>1</v>
@@ -1059,10 +1059,10 @@
         <v>2</v>
       </c>
       <c r="F19" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G19" s="10">
-        <v>51365</v>
+        <v>51837</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1122,16 +1122,16 @@
         <v>8</v>
       </c>
       <c r="D22" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" s="10">
         <v>3</v>
       </c>
       <c r="F22" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" s="10">
-        <v>130471</v>
+        <v>146967</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1164,11 +1164,11 @@
       <c r="B24" s="5"/>
       <c r="C24" s="6">
         <f>SUM(C3:C23)</f>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D24" s="6">
         <f>SUM(D3:D23)</f>
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E24" s="6">
         <f>SUM(E3:E23)</f>
@@ -1176,11 +1176,11 @@
       </c>
       <c r="F24" s="6">
         <f>SUM(F3:F23)</f>
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G24" s="6">
         <f>SUM(G3:G23)</f>
-        <v>2020400</v>
+        <v>2042159</v>
       </c>
     </row>
   </sheetData>
@@ -1258,10 +1258,10 @@
         <v>31</v>
       </c>
       <c r="C3" s="10">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D3" s="10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" s="10">
         <v>19</v>
@@ -1270,7 +1270,7 @@
         <v>81</v>
       </c>
       <c r="G3" s="10">
-        <v>349447</v>
+        <v>384195</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1281,19 +1281,19 @@
         <v>31</v>
       </c>
       <c r="C4" s="10">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D4" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="10">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G4" s="10">
-        <v>456535</v>
+        <v>460335</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1316,7 +1316,7 @@
         <v>76</v>
       </c>
       <c r="G5" s="10">
-        <v>603857</v>
+        <v>608062</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1327,7 +1327,7 @@
         <v>31</v>
       </c>
       <c r="C6" s="10">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D6" s="10">
         <v>0</v>
@@ -1336,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="10">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G6" s="10">
         <v>75787</v>
@@ -1350,7 +1350,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="10">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D7" s="10">
         <v>24</v>
@@ -1359,10 +1359,10 @@
         <v>19</v>
       </c>
       <c r="F7" s="10">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G7" s="10">
-        <v>3045072</v>
+        <v>3050362</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1385,7 +1385,7 @@
         <v>283</v>
       </c>
       <c r="G8" s="10">
-        <v>1081355</v>
+        <v>1081771</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1431,7 +1431,7 @@
         <v>113</v>
       </c>
       <c r="G10" s="10">
-        <v>757310</v>
+        <v>773473</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1465,7 +1465,7 @@
         <v>31</v>
       </c>
       <c r="C12" s="10">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D12" s="10">
         <v>31</v>
@@ -1474,10 +1474,10 @@
         <v>23</v>
       </c>
       <c r="F12" s="10">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G12" s="10">
-        <v>1943387</v>
+        <v>1949084</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1488,10 +1488,10 @@
         <v>31</v>
       </c>
       <c r="C13" s="10">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D13" s="10">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13" s="10">
         <v>19</v>
@@ -1500,7 +1500,7 @@
         <v>135</v>
       </c>
       <c r="G13" s="10">
-        <v>916984</v>
+        <v>979930</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1514,16 +1514,16 @@
         <v>430</v>
       </c>
       <c r="D14" s="10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" s="10">
         <v>13</v>
       </c>
       <c r="F14" s="10">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G14" s="10">
-        <v>615396</v>
+        <v>626890</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1534,19 +1534,19 @@
         <v>31</v>
       </c>
       <c r="C15" s="10">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D15" s="10">
         <v>26</v>
       </c>
       <c r="E15" s="10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F15" s="10">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G15" s="10">
-        <v>1023459</v>
+        <v>1029983</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1569,7 +1569,7 @@
         <v>281</v>
       </c>
       <c r="G16" s="10">
-        <v>1309416</v>
+        <v>1319028</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1592,7 +1592,7 @@
         <v>269</v>
       </c>
       <c r="G17" s="10">
-        <v>3908257</v>
+        <v>3910049</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1603,19 +1603,19 @@
         <v>31</v>
       </c>
       <c r="C18" s="10">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" s="10">
         <v>4</v>
       </c>
       <c r="E18" s="10">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F18" s="10">
         <v>73</v>
       </c>
       <c r="G18" s="10">
-        <v>296533</v>
+        <v>311141</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1626,19 +1626,19 @@
         <v>31</v>
       </c>
       <c r="C19" s="10">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D19" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="10">
         <v>15</v>
       </c>
       <c r="F19" s="10">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G19" s="10">
-        <v>745368</v>
+        <v>751566</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1649,19 +1649,19 @@
         <v>31</v>
       </c>
       <c r="C20" s="10">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D20" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="10">
         <v>21</v>
       </c>
       <c r="F20" s="10">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G20" s="10">
-        <v>149308</v>
+        <v>159536</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1672,7 +1672,7 @@
         <v>31</v>
       </c>
       <c r="C21" s="10">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D21" s="10">
         <v>22</v>
@@ -1681,10 +1681,10 @@
         <v>11</v>
       </c>
       <c r="F21" s="10">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G21" s="10">
-        <v>1077922</v>
+        <v>1078784</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1695,7 +1695,7 @@
         <v>31</v>
       </c>
       <c r="C22" s="10">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D22" s="10">
         <v>27</v>
@@ -1704,10 +1704,10 @@
         <v>22</v>
       </c>
       <c r="F22" s="10">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G22" s="10">
-        <v>1218083</v>
+        <v>1221394</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1740,23 +1740,23 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4351</v>
+        <v>4369</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5110</v>
+        <v>5124</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>24912875</v>
+        <v>25110769</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B514E5B-7199-4E77-9A17-0538452BF155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA6E1C8-564E-4502-8E31-80DBD130508B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -319,10 +319,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -641,15 +641,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -869,16 +869,16 @@
         <v>15</v>
       </c>
       <c r="D11" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="10">
         <v>0</v>
       </c>
       <c r="F11" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G11" s="10">
-        <v>309506</v>
+        <v>309955</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D24" s="6">
         <f>SUM(D3:D23)</f>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E24" s="6">
         <f>SUM(E3:E23)</f>
@@ -1176,11 +1176,11 @@
       </c>
       <c r="F24" s="6">
         <f>SUM(F3:F23)</f>
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G24" s="6">
         <f>SUM(G3:G23)</f>
-        <v>2042159</v>
+        <v>2042608</v>
       </c>
     </row>
   </sheetData>
@@ -1217,15 +1217,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1258,7 +1258,7 @@
         <v>31</v>
       </c>
       <c r="C3" s="10">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3" s="10">
         <v>6</v>
@@ -1267,10 +1267,10 @@
         <v>19</v>
       </c>
       <c r="F3" s="10">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G3" s="10">
-        <v>384195</v>
+        <v>386506</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1304,19 +1304,19 @@
         <v>31</v>
       </c>
       <c r="C5" s="10">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" s="10">
         <v>18</v>
       </c>
       <c r="F5" s="10">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G5" s="10">
-        <v>608062</v>
+        <v>694394</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1327,7 +1327,7 @@
         <v>31</v>
       </c>
       <c r="C6" s="10">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D6" s="10">
         <v>0</v>
@@ -1336,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="10">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G6" s="10">
         <v>75787</v>
@@ -1373,7 +1373,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="10">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D8" s="10">
         <v>17</v>
@@ -1382,10 +1382,10 @@
         <v>28</v>
       </c>
       <c r="F8" s="10">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G8" s="10">
-        <v>1081771</v>
+        <v>1094452</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1419,7 +1419,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="10">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D10" s="10">
         <v>19</v>
@@ -1428,10 +1428,10 @@
         <v>22</v>
       </c>
       <c r="F10" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G10" s="10">
-        <v>773473</v>
+        <v>774713</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1445,16 +1445,16 @@
         <v>317</v>
       </c>
       <c r="D11" s="10">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E11" s="10">
         <v>21</v>
       </c>
       <c r="F11" s="10">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G11" s="10">
-        <v>5013879</v>
+        <v>5045335</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1500,7 +1500,7 @@
         <v>135</v>
       </c>
       <c r="G13" s="10">
-        <v>979930</v>
+        <v>991639</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1511,19 +1511,19 @@
         <v>31</v>
       </c>
       <c r="C14" s="10">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D14" s="10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" s="10">
         <v>13</v>
       </c>
       <c r="F14" s="10">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G14" s="10">
-        <v>626890</v>
+        <v>628075</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1534,19 +1534,19 @@
         <v>31</v>
       </c>
       <c r="C15" s="10">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D15" s="10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" s="10">
         <v>13</v>
       </c>
       <c r="F15" s="10">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G15" s="10">
-        <v>1029983</v>
+        <v>1041602</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1569,7 +1569,7 @@
         <v>281</v>
       </c>
       <c r="G16" s="10">
-        <v>1319028</v>
+        <v>1326739</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1592,7 +1592,7 @@
         <v>269</v>
       </c>
       <c r="G17" s="10">
-        <v>3910049</v>
+        <v>3916783</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1603,19 +1603,19 @@
         <v>31</v>
       </c>
       <c r="C18" s="10">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" s="10">
         <v>4</v>
       </c>
       <c r="E18" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F18" s="10">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G18" s="10">
-        <v>311141</v>
+        <v>313340</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1672,7 +1672,7 @@
         <v>31</v>
       </c>
       <c r="C21" s="10">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D21" s="10">
         <v>22</v>
@@ -1681,10 +1681,10 @@
         <v>11</v>
       </c>
       <c r="F21" s="10">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="G21" s="10">
-        <v>1078784</v>
+        <v>1080097</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1740,23 +1740,23 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4369</v>
+        <v>4379</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5124</v>
+        <v>5139</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>25110769</v>
+        <v>25287259</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA6E1C8-564E-4502-8E31-80DBD130508B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77A790E-D69E-4EFD-8A76-92EE605D82B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -319,10 +319,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -641,15 +641,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1217,15 +1217,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1281,10 +1281,10 @@
         <v>31</v>
       </c>
       <c r="C4" s="10">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D4" s="10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="10">
         <v>17</v>
@@ -1293,7 +1293,7 @@
         <v>301</v>
       </c>
       <c r="G4" s="10">
-        <v>460335</v>
+        <v>460990</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1316,7 +1316,7 @@
         <v>78</v>
       </c>
       <c r="G5" s="10">
-        <v>694394</v>
+        <v>698297</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1362,7 +1362,7 @@
         <v>319</v>
       </c>
       <c r="G7" s="10">
-        <v>3050362</v>
+        <v>3056396</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1373,10 +1373,10 @@
         <v>31</v>
       </c>
       <c r="C8" s="10">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D8" s="10">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="10">
         <v>28</v>
@@ -1385,7 +1385,7 @@
         <v>284</v>
       </c>
       <c r="G8" s="10">
-        <v>1094452</v>
+        <v>1103493</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1425,10 +1425,10 @@
         <v>19</v>
       </c>
       <c r="E10" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10" s="10">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G10" s="10">
         <v>774713</v>
@@ -1557,19 +1557,19 @@
         <v>31</v>
       </c>
       <c r="C16" s="10">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D16" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16" s="10">
         <v>19</v>
       </c>
       <c r="F16" s="10">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G16" s="10">
-        <v>1326739</v>
+        <v>1334108</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1592,7 +1592,7 @@
         <v>269</v>
       </c>
       <c r="G17" s="10">
-        <v>3916783</v>
+        <v>3922875</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1626,10 +1626,10 @@
         <v>31</v>
       </c>
       <c r="C19" s="10">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D19" s="10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="10">
         <v>15</v>
@@ -1638,7 +1638,7 @@
         <v>307</v>
       </c>
       <c r="G19" s="10">
-        <v>751566</v>
+        <v>751747</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1740,23 +1740,23 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4379</v>
+        <v>4383</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5139</v>
+        <v>5142</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>25287259</v>
+        <v>25320534</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77A790E-D69E-4EFD-8A76-92EE605D82B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1560BC3-8B37-4CC1-852B-F890BAAFA7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
     <sheet name="🟢 e2open Data" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -319,10 +319,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -641,15 +641,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -708,16 +708,16 @@
         <v>7</v>
       </c>
       <c r="D4" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="10">
         <v>1</v>
       </c>
       <c r="F4" s="10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" s="10">
-        <v>115935</v>
+        <v>115713</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -912,19 +912,19 @@
         <v>31</v>
       </c>
       <c r="C13" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" s="10">
         <v>1</v>
       </c>
       <c r="F13" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G13" s="10">
-        <v>116608</v>
+        <v>200199</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -984,16 +984,16 @@
         <v>3</v>
       </c>
       <c r="D16" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="10">
         <v>1</v>
       </c>
       <c r="F16" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16" s="10">
-        <v>62170</v>
+        <v>62127</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1007,16 +1007,16 @@
         <v>0</v>
       </c>
       <c r="D17" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="10">
         <v>1</v>
       </c>
       <c r="F17" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G17" s="10">
-        <v>39210</v>
+        <v>30817</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1053,16 +1053,16 @@
         <v>13</v>
       </c>
       <c r="D19" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="10">
         <v>2</v>
       </c>
       <c r="F19" s="10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G19" s="10">
-        <v>51837</v>
+        <v>50837</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1119,19 +1119,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" s="10">
         <v>3</v>
       </c>
       <c r="F22" s="10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22" s="10">
-        <v>146967</v>
+        <v>158154</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1148,10 +1148,10 @@
         <v>7</v>
       </c>
       <c r="E23" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" s="10">
         <v>55060</v>
@@ -1164,23 +1164,23 @@
       <c r="B24" s="5"/>
       <c r="C24" s="6">
         <f>SUM(C3:C23)</f>
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D24" s="6">
         <f>SUM(D3:D23)</f>
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E24" s="6">
         <f>SUM(E3:E23)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F24" s="6">
         <f>SUM(F3:F23)</f>
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G24" s="6">
         <f>SUM(G3:G23)</f>
-        <v>2042608</v>
+        <v>2127728</v>
       </c>
     </row>
   </sheetData>
@@ -1217,15 +1217,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1281,19 +1281,19 @@
         <v>31</v>
       </c>
       <c r="C4" s="10">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D4" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="10">
         <v>17</v>
       </c>
       <c r="F4" s="10">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G4" s="10">
-        <v>460990</v>
+        <v>465227</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1350,7 +1350,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="10">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D7" s="10">
         <v>24</v>
@@ -1359,10 +1359,10 @@
         <v>19</v>
       </c>
       <c r="F7" s="10">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G7" s="10">
-        <v>3056396</v>
+        <v>3063848</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1373,19 +1373,19 @@
         <v>31</v>
       </c>
       <c r="C8" s="10">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D8" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" s="10">
         <v>28</v>
       </c>
       <c r="F8" s="10">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G8" s="10">
-        <v>1103493</v>
+        <v>1143981</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1419,19 +1419,19 @@
         <v>31</v>
       </c>
       <c r="C10" s="10">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D10" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" s="10">
         <v>23</v>
       </c>
       <c r="F10" s="10">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G10" s="10">
-        <v>774713</v>
+        <v>798536</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1442,7 +1442,7 @@
         <v>31</v>
       </c>
       <c r="C11" s="10">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D11" s="10">
         <v>46</v>
@@ -1451,10 +1451,10 @@
         <v>21</v>
       </c>
       <c r="F11" s="10">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="G11" s="10">
-        <v>5045335</v>
+        <v>5076370</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1465,19 +1465,19 @@
         <v>31</v>
       </c>
       <c r="C12" s="10">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D12" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" s="10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F12" s="10">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G12" s="10">
-        <v>1949084</v>
+        <v>1972604</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1488,19 +1488,19 @@
         <v>31</v>
       </c>
       <c r="C13" s="10">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D13" s="10">
         <v>37</v>
       </c>
       <c r="E13" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13" s="10">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G13" s="10">
-        <v>991639</v>
+        <v>1008033</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1511,19 +1511,19 @@
         <v>31</v>
       </c>
       <c r="C14" s="10">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D14" s="10">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E14" s="10">
         <v>13</v>
       </c>
       <c r="F14" s="10">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G14" s="10">
-        <v>628075</v>
+        <v>634448</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1534,7 +1534,7 @@
         <v>31</v>
       </c>
       <c r="C15" s="10">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D15" s="10">
         <v>27</v>
@@ -1543,10 +1543,10 @@
         <v>13</v>
       </c>
       <c r="F15" s="10">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G15" s="10">
-        <v>1041602</v>
+        <v>1042483</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1557,19 +1557,19 @@
         <v>31</v>
       </c>
       <c r="C16" s="10">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D16" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E16" s="10">
         <v>19</v>
       </c>
       <c r="F16" s="10">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G16" s="10">
-        <v>1334108</v>
+        <v>1352288</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1580,19 +1580,19 @@
         <v>31</v>
       </c>
       <c r="C17" s="10">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D17" s="10">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E17" s="10">
         <v>25</v>
       </c>
       <c r="F17" s="10">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="G17" s="10">
-        <v>3922875</v>
+        <v>3974323</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1626,19 +1626,19 @@
         <v>31</v>
       </c>
       <c r="C19" s="10">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D19" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="10">
         <v>15</v>
       </c>
       <c r="F19" s="10">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G19" s="10">
-        <v>751747</v>
+        <v>756309</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1655,13 +1655,13 @@
         <v>2</v>
       </c>
       <c r="E20" s="10">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F20" s="10">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G20" s="10">
-        <v>159536</v>
+        <v>161344</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1672,19 +1672,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="10">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D21" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E21" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" s="10">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G21" s="10">
-        <v>1080097</v>
+        <v>1083071</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1695,19 +1695,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="10">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D22" s="10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E22" s="10">
         <v>22</v>
       </c>
       <c r="F22" s="10">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="G22" s="10">
-        <v>1221394</v>
+        <v>1261792</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1718,19 +1718,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="10">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D23" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E23" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F23" s="10">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G23" s="10">
-        <v>296588</v>
+        <v>323860</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1740,23 +1740,23 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4383</v>
+        <v>4414</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5142</v>
+        <v>5192</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>25320534</v>
+        <v>25621379</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1560BC3-8B37-4CC1-852B-F890BAAFA7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FFBE31-09CA-4763-BF33-2D279DE85C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -319,10 +319,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -641,15 +641,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -832,7 +832,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="10">
-        <v>26136</v>
+        <v>29083</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1142,7 +1142,7 @@
         <v>31</v>
       </c>
       <c r="C23" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="10">
         <v>7</v>
@@ -1151,10 +1151,10 @@
         <v>2</v>
       </c>
       <c r="F23" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23" s="10">
-        <v>55060</v>
+        <v>56280</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1164,7 +1164,7 @@
       <c r="B24" s="5"/>
       <c r="C24" s="6">
         <f>SUM(C3:C23)</f>
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D24" s="6">
         <f>SUM(D3:D23)</f>
@@ -1176,11 +1176,11 @@
       </c>
       <c r="F24" s="6">
         <f>SUM(F3:F23)</f>
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G24" s="6">
         <f>SUM(G3:G23)</f>
-        <v>2127728</v>
+        <v>2131895</v>
       </c>
     </row>
   </sheetData>
@@ -1217,15 +1217,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1258,19 +1258,19 @@
         <v>31</v>
       </c>
       <c r="C3" s="10">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3" s="10">
         <v>6</v>
       </c>
       <c r="E3" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="10">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G3" s="10">
-        <v>386506</v>
+        <v>387574</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1281,19 +1281,19 @@
         <v>31</v>
       </c>
       <c r="C4" s="10">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D4" s="10">
         <v>15</v>
       </c>
       <c r="E4" s="10">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" s="10">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G4" s="10">
-        <v>465227</v>
+        <v>468930</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1304,7 +1304,7 @@
         <v>31</v>
       </c>
       <c r="C5" s="10">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" s="10">
         <v>10</v>
@@ -1313,10 +1313,10 @@
         <v>18</v>
       </c>
       <c r="F5" s="10">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" s="10">
-        <v>698297</v>
+        <v>700336</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1327,7 +1327,7 @@
         <v>31</v>
       </c>
       <c r="C6" s="10">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D6" s="10">
         <v>0</v>
@@ -1336,10 +1336,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="10">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="G6" s="10">
-        <v>75787</v>
+        <v>75795</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1350,19 +1350,19 @@
         <v>31</v>
       </c>
       <c r="C7" s="10">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D7" s="10">
         <v>24</v>
       </c>
       <c r="E7" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="10">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G7" s="10">
-        <v>3063848</v>
+        <v>3108709</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1373,19 +1373,19 @@
         <v>31</v>
       </c>
       <c r="C8" s="10">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D8" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="10">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F8" s="10">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G8" s="10">
-        <v>1143981</v>
+        <v>1167302</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1399,16 +1399,16 @@
         <v>0</v>
       </c>
       <c r="D9" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G9" s="10">
-        <v>28932</v>
+        <v>38815</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1419,19 +1419,19 @@
         <v>31</v>
       </c>
       <c r="C10" s="10">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D10" s="10">
         <v>20</v>
       </c>
       <c r="E10" s="10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F10" s="10">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G10" s="10">
-        <v>798536</v>
+        <v>837097</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1442,19 +1442,19 @@
         <v>31</v>
       </c>
       <c r="C11" s="10">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D11" s="10">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" s="10">
         <v>21</v>
       </c>
       <c r="F11" s="10">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="G11" s="10">
-        <v>5076370</v>
+        <v>5192607</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1465,19 +1465,19 @@
         <v>31</v>
       </c>
       <c r="C12" s="10">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D12" s="10">
         <v>32</v>
       </c>
       <c r="E12" s="10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F12" s="10">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="G12" s="10">
-        <v>1972604</v>
+        <v>2038298</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1488,19 +1488,19 @@
         <v>31</v>
       </c>
       <c r="C13" s="10">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D13" s="10">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E13" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F13" s="10">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G13" s="10">
-        <v>1008033</v>
+        <v>1083730</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1511,19 +1511,19 @@
         <v>31</v>
       </c>
       <c r="C14" s="10">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="D14" s="10">
         <v>35</v>
       </c>
       <c r="E14" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="10">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="G14" s="10">
-        <v>634448</v>
+        <v>640213</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1534,7 +1534,7 @@
         <v>31</v>
       </c>
       <c r="C15" s="10">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="D15" s="10">
         <v>27</v>
@@ -1543,10 +1543,10 @@
         <v>13</v>
       </c>
       <c r="F15" s="10">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="G15" s="10">
-        <v>1042483</v>
+        <v>1073653</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1557,19 +1557,19 @@
         <v>31</v>
       </c>
       <c r="C16" s="10">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D16" s="10">
         <v>20</v>
       </c>
       <c r="E16" s="10">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F16" s="10">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G16" s="10">
-        <v>1352288</v>
+        <v>1368772</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1583,16 +1583,16 @@
         <v>214</v>
       </c>
       <c r="D17" s="10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E17" s="10">
         <v>25</v>
       </c>
       <c r="F17" s="10">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G17" s="10">
-        <v>3974323</v>
+        <v>4070090</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1626,19 +1626,19 @@
         <v>31</v>
       </c>
       <c r="C19" s="10">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D19" s="10">
         <v>12</v>
       </c>
       <c r="E19" s="10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F19" s="10">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G19" s="10">
-        <v>756309</v>
+        <v>768433</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1649,7 +1649,7 @@
         <v>31</v>
       </c>
       <c r="C20" s="10">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D20" s="10">
         <v>2</v>
@@ -1658,10 +1658,10 @@
         <v>23</v>
       </c>
       <c r="F20" s="10">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G20" s="10">
-        <v>161344</v>
+        <v>178017</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1672,19 +1672,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="10">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D21" s="10">
         <v>23</v>
       </c>
       <c r="E21" s="10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F21" s="10">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="G21" s="10">
-        <v>1083071</v>
+        <v>1144874</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1695,19 +1695,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="10">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="D22" s="10">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E22" s="10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F22" s="10">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="G22" s="10">
-        <v>1261792</v>
+        <v>1283682</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1718,19 +1718,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="10">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D23" s="10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E23" s="10">
         <v>15</v>
       </c>
       <c r="F23" s="10">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G23" s="10">
-        <v>323860</v>
+        <v>328377</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1740,23 +1740,23 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4414</v>
+        <v>4481</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5192</v>
+        <v>5265</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>25621379</v>
+        <v>26268644</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FFBE31-09CA-4763-BF33-2D279DE85C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6FF8D1-6198-4BD7-A352-46D5B1DC5F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -1264,10 +1264,10 @@
         <v>6</v>
       </c>
       <c r="E3" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="10">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3" s="10">
         <v>387574</v>
@@ -1281,19 +1281,19 @@
         <v>31</v>
       </c>
       <c r="C4" s="10">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D4" s="10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F4" s="10">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G4" s="10">
-        <v>468930</v>
+        <v>470355</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1310,13 +1310,13 @@
         <v>10</v>
       </c>
       <c r="E5" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="10">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G5" s="10">
-        <v>700336</v>
+        <v>754141</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1327,7 +1327,7 @@
         <v>31</v>
       </c>
       <c r="C6" s="10">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D6" s="10">
         <v>0</v>
@@ -1336,10 +1336,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="10">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G6" s="10">
-        <v>75795</v>
+        <v>75847</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1350,19 +1350,19 @@
         <v>31</v>
       </c>
       <c r="C7" s="10">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D7" s="10">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E7" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="10">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G7" s="10">
-        <v>3108709</v>
+        <v>3136278</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1379,10 +1379,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="10">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G8" s="10">
         <v>1167302</v>
@@ -1396,10 +1396,10 @@
         <v>31</v>
       </c>
       <c r="C9" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="10">
         <v>2</v>
@@ -1408,7 +1408,7 @@
         <v>9</v>
       </c>
       <c r="G9" s="10">
-        <v>38815</v>
+        <v>62082</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1419,7 +1419,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="10">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D10" s="10">
         <v>20</v>
@@ -1428,10 +1428,10 @@
         <v>25</v>
       </c>
       <c r="F10" s="10">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G10" s="10">
-        <v>837097</v>
+        <v>863351</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1442,19 +1442,19 @@
         <v>31</v>
       </c>
       <c r="C11" s="10">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D11" s="10">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E11" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11" s="10">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="G11" s="10">
-        <v>5192607</v>
+        <v>5283024</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1465,19 +1465,19 @@
         <v>31</v>
       </c>
       <c r="C12" s="10">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D12" s="10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12" s="10">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G12" s="10">
-        <v>2038298</v>
+        <v>2057413</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1488,19 +1488,19 @@
         <v>31</v>
       </c>
       <c r="C13" s="10">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D13" s="10">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" s="10">
         <v>21</v>
       </c>
       <c r="F13" s="10">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G13" s="10">
-        <v>1083730</v>
+        <v>1183123</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1511,19 +1511,19 @@
         <v>31</v>
       </c>
       <c r="C14" s="10">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D14" s="10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F14" s="10">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="G14" s="10">
-        <v>640213</v>
+        <v>651185</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1534,19 +1534,19 @@
         <v>31</v>
       </c>
       <c r="C15" s="10">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D15" s="10">
         <v>27</v>
       </c>
       <c r="E15" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F15" s="10">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="G15" s="10">
-        <v>1073653</v>
+        <v>1074105</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1560,16 +1560,16 @@
         <v>251</v>
       </c>
       <c r="D16" s="10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F16" s="10">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G16" s="10">
-        <v>1368772</v>
+        <v>1368729</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1583,16 +1583,16 @@
         <v>214</v>
       </c>
       <c r="D17" s="10">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="10">
         <v>277</v>
       </c>
       <c r="G17" s="10">
-        <v>4070090</v>
+        <v>4087682</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1609,10 +1609,10 @@
         <v>4</v>
       </c>
       <c r="E18" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F18" s="10">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G18" s="10">
         <v>313340</v>
@@ -1632,13 +1632,13 @@
         <v>12</v>
       </c>
       <c r="E19" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F19" s="10">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G19" s="10">
-        <v>768433</v>
+        <v>795339</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1655,10 +1655,10 @@
         <v>2</v>
       </c>
       <c r="E20" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20" s="10">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G20" s="10">
         <v>178017</v>
@@ -1672,19 +1672,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="10">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D21" s="10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E21" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F21" s="10">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="G21" s="10">
-        <v>1144874</v>
+        <v>1146572</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1695,19 +1695,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="10">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D22" s="10">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E22" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F22" s="10">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G22" s="10">
-        <v>1283682</v>
+        <v>1291818</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1718,7 +1718,7 @@
         <v>31</v>
       </c>
       <c r="C23" s="10">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D23" s="10">
         <v>15</v>
@@ -1727,10 +1727,10 @@
         <v>15</v>
       </c>
       <c r="F23" s="10">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G23" s="10">
-        <v>328377</v>
+        <v>329937</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1740,23 +1740,23 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4481</v>
+        <v>4514</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5265</v>
+        <v>5310</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>26268644</v>
+        <v>26677214</v>
       </c>
     </row>
   </sheetData>

--- a/AI_Course_Dashboard_Data.xlsx
+++ b/AI_Course_Dashboard_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadhana.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6FF8D1-6198-4BD7-A352-46D5B1DC5F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70A5AEF-86C4-4102-BC0D-61F50DCEA050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🔵 WTG Data" sheetId="3" r:id="rId1"/>
@@ -319,10 +319,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -641,15 +641,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1217,15 +1217,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1281,19 +1281,19 @@
         <v>31</v>
       </c>
       <c r="C4" s="10">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D4" s="10">
         <v>14</v>
       </c>
       <c r="E4" s="10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="10">
         <v>309</v>
       </c>
       <c r="G4" s="10">
-        <v>470355</v>
+        <v>470477</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1350,19 +1350,19 @@
         <v>31</v>
       </c>
       <c r="C7" s="10">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D7" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" s="10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F7" s="10">
         <v>327</v>
       </c>
       <c r="G7" s="10">
-        <v>3136278</v>
+        <v>3155314</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1373,19 +1373,19 @@
         <v>31</v>
       </c>
       <c r="C8" s="10">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D8" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F8" s="10">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G8" s="10">
-        <v>1167302</v>
+        <v>1178542</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1419,19 +1419,19 @@
         <v>31</v>
       </c>
       <c r="C10" s="10">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D10" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="10">
         <v>25</v>
       </c>
       <c r="F10" s="10">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G10" s="10">
-        <v>863351</v>
+        <v>876808</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1442,19 +1442,19 @@
         <v>31</v>
       </c>
       <c r="C11" s="10">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D11" s="10">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11" s="10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11" s="10">
         <v>395</v>
       </c>
       <c r="G11" s="10">
-        <v>5283024</v>
+        <v>5310709</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1465,19 +1465,19 @@
         <v>31</v>
       </c>
       <c r="C12" s="10">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D12" s="10">
         <v>31</v>
       </c>
       <c r="E12" s="10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" s="10">
         <v>342</v>
       </c>
       <c r="G12" s="10">
-        <v>2057413</v>
+        <v>2057858</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1511,19 +1511,19 @@
         <v>31</v>
       </c>
       <c r="C14" s="10">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D14" s="10">
         <v>36</v>
       </c>
       <c r="E14" s="10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F14" s="10">
         <v>493</v>
       </c>
       <c r="G14" s="10">
-        <v>651185</v>
+        <v>651378</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1534,19 +1534,19 @@
         <v>31</v>
       </c>
       <c r="C15" s="10">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D15" s="10">
         <v>27</v>
       </c>
       <c r="E15" s="10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F15" s="10">
         <v>382</v>
       </c>
       <c r="G15" s="10">
-        <v>1074105</v>
+        <v>1074477</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1557,19 +1557,19 @@
         <v>31</v>
       </c>
       <c r="C16" s="10">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D16" s="10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E16" s="10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F16" s="10">
         <v>289</v>
       </c>
       <c r="G16" s="10">
-        <v>1368729</v>
+        <v>1372284</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1580,19 +1580,19 @@
         <v>31</v>
       </c>
       <c r="C17" s="10">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D17" s="10">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17" s="10">
         <v>26</v>
       </c>
       <c r="F17" s="10">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G17" s="10">
-        <v>4087682</v>
+        <v>4126436</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1626,19 +1626,19 @@
         <v>31</v>
       </c>
       <c r="C19" s="10">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D19" s="10">
         <v>12</v>
       </c>
       <c r="E19" s="10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F19" s="10">
         <v>314</v>
       </c>
       <c r="G19" s="10">
-        <v>795339</v>
+        <v>797083</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1672,19 +1672,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="10">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D21" s="10">
         <v>22</v>
       </c>
       <c r="E21" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F21" s="10">
         <v>446</v>
       </c>
       <c r="G21" s="10">
-        <v>1146572</v>
+        <v>1148249</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1740,7 +1740,7 @@
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <f>SUM(C3:C23)</f>
-        <v>4514</v>
+        <v>4530</v>
       </c>
       <c r="D24" s="9">
         <f>SUM(D3:D23)</f>
@@ -1748,15 +1748,15 @@
       </c>
       <c r="E24" s="9">
         <f>SUM(E3:E23)</f>
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="F24" s="9">
         <f>SUM(F3:F23)</f>
-        <v>5310</v>
+        <v>5315</v>
       </c>
       <c r="G24" s="9">
         <f>SUM(G3:G23)</f>
-        <v>26677214</v>
+        <v>26795494</v>
       </c>
     </row>
   </sheetData>
